--- a/2_Raw_Data/2_1_TPS/R1_target_population.xlsx
+++ b/2_Raw_Data/2_1_TPS/R1_target_population.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liuwe\Desktop\大团队科学样本代表性\BTS_Sample_Stage1_RR\BTS_Sample_Stage1_RR\2_Raw_Data\2_1_TPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825E3BE5-A9BD-4C61-B440-3321DEB929C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A067C18-C094-4D90-99A6-FE8D753DD38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8070,7 +8070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L691"/>
+  <dimension ref="A1:K691"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="8.796875" style="9"/>
@@ -8084,7 +8084,7 @@
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="32" t="s">
         <v>1255</v>
       </c>
@@ -8119,7 +8119,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:11">
       <c r="A2" s="9">
         <v>24010002</v>
       </c>
@@ -8153,11 +8153,8 @@
       <c r="K2" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L2" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="9">
         <v>24010004</v>
       </c>
@@ -8192,7 +8189,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:11">
       <c r="A4" s="9">
         <v>24010005</v>
       </c>
@@ -8221,7 +8218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:11">
       <c r="A5" s="9">
         <v>24010006</v>
       </c>
@@ -8256,7 +8253,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:11">
       <c r="A6" s="9">
         <v>24010007</v>
       </c>
@@ -8291,7 +8288,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15">
+    <row r="7" spans="1:11" ht="15">
       <c r="A7" s="9">
         <v>24010008</v>
       </c>
@@ -8325,9 +8322,8 @@
       <c r="K7" s="9" t="s">
         <v>1679</v>
       </c>
-      <c r="L7" s="9"/>
-    </row>
-    <row r="8" spans="1:12">
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="9">
         <v>24010010</v>
       </c>
@@ -8361,11 +8357,8 @@
       <c r="K8" s="9" t="s">
         <v>1504</v>
       </c>
-      <c r="L8" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="9">
         <v>24010012</v>
       </c>
@@ -8399,11 +8392,8 @@
       <c r="K9" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L9" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="9">
         <v>24010013</v>
       </c>
@@ -8437,11 +8427,8 @@
       <c r="K10" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L10" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="9">
         <v>24010014</v>
       </c>
@@ -8476,7 +8463,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:11">
       <c r="A12" s="9">
         <v>24010015</v>
       </c>
@@ -8511,7 +8498,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:11">
       <c r="A13" s="9">
         <v>24010016</v>
       </c>
@@ -8545,9 +8532,8 @@
       <c r="K13" s="9" t="s">
         <v>1432</v>
       </c>
-      <c r="L13" s="9"/>
-    </row>
-    <row r="14" spans="1:12">
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="9">
         <v>24010017</v>
       </c>
@@ -8581,9 +8567,8 @@
       <c r="K14" s="9" t="s">
         <v>1644</v>
       </c>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="1:12">
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="9">
         <v>24010018</v>
       </c>
@@ -8618,7 +8603,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:11">
       <c r="A16" s="9">
         <v>24010019</v>
       </c>
@@ -8652,9 +8637,8 @@
       <c r="K16" s="9" t="s">
         <v>1555</v>
       </c>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="1:12">
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="9">
         <v>24010021</v>
       </c>
@@ -8688,11 +8672,8 @@
       <c r="K17" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L17" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="9">
         <v>24010022</v>
       </c>
@@ -8726,11 +8707,8 @@
       <c r="K18" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L18" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="9">
         <v>24010024</v>
       </c>
@@ -8762,7 +8740,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:11">
       <c r="A20" s="9">
         <v>24010025</v>
       </c>
@@ -8796,9 +8774,8 @@
       <c r="K20" s="9" t="s">
         <v>1700</v>
       </c>
-      <c r="L20" s="9"/>
-    </row>
-    <row r="21" spans="1:12">
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="9">
         <v>24010026</v>
       </c>
@@ -8832,9 +8809,8 @@
       <c r="K21" s="9" t="s">
         <v>1707</v>
       </c>
-      <c r="L21" s="9"/>
-    </row>
-    <row r="22" spans="1:12">
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="9">
         <v>24010029</v>
       </c>
@@ -8866,7 +8842,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:11">
       <c r="A23" s="9">
         <v>24010030</v>
       </c>
@@ -8901,7 +8877,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.6" customHeight="1">
+    <row r="24" spans="1:11" ht="15.6" customHeight="1">
       <c r="A24" s="9">
         <v>24010031</v>
       </c>
@@ -8936,7 +8912,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="10" customFormat="1" ht="15">
+    <row r="25" spans="1:11" s="10" customFormat="1" ht="15">
       <c r="A25" s="9">
         <v>24010032</v>
       </c>
@@ -8970,11 +8946,8 @@
       <c r="K25" s="9" t="s">
         <v>1759</v>
       </c>
-      <c r="L25" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="51">
         <v>24010034</v>
       </c>
@@ -9008,11 +8981,8 @@
       <c r="K26" s="51" t="s">
         <v>1892</v>
       </c>
-      <c r="L26" s="51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15">
+    </row>
+    <row r="27" spans="1:11" ht="15">
       <c r="A27" s="9">
         <v>24010035</v>
       </c>
@@ -9046,11 +9016,8 @@
       <c r="K27" s="9" t="s">
         <v>2010</v>
       </c>
-      <c r="L27" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="9">
         <v>24010036</v>
       </c>
@@ -9084,11 +9051,8 @@
       <c r="K28" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="L28" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="9">
         <v>24010037</v>
       </c>
@@ -9123,7 +9087,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:11">
       <c r="A30" s="9">
         <v>24010038</v>
       </c>
@@ -9158,7 +9122,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:11">
       <c r="A31" s="9">
         <v>24010039</v>
       </c>
@@ -9193,7 +9157,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="9" customFormat="1">
+    <row r="32" spans="1:11" s="9" customFormat="1">
       <c r="A32" s="9">
         <v>24010040</v>
       </c>
@@ -9227,11 +9191,8 @@
       <c r="K32" s="9" t="s">
         <v>790</v>
       </c>
-      <c r="L32" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="9">
         <v>24010041</v>
       </c>
@@ -9265,9 +9226,8 @@
       <c r="K33" s="9" t="s">
         <v>1549</v>
       </c>
-      <c r="L33" s="9"/>
-    </row>
-    <row r="34" spans="1:12">
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="9">
         <v>24010044</v>
       </c>
@@ -9302,7 +9262,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:11">
       <c r="A35" s="9">
         <v>24010045</v>
       </c>
@@ -9337,7 +9297,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:11">
       <c r="A36" s="9">
         <v>24010046</v>
       </c>
@@ -9372,7 +9332,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:11">
       <c r="A37" s="9">
         <v>24010047</v>
       </c>
@@ -9404,9 +9364,8 @@
         <v>1</v>
       </c>
       <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-    </row>
-    <row r="38" spans="1:12">
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="9">
         <v>24010048</v>
       </c>
@@ -9441,7 +9400,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:11">
       <c r="A39" s="9">
         <v>24010051</v>
       </c>
@@ -9475,9 +9434,8 @@
       <c r="K39" s="9" t="s">
         <v>1623</v>
       </c>
-      <c r="L39" s="9"/>
-    </row>
-    <row r="40" spans="1:12">
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="9">
         <v>24010053</v>
       </c>
@@ -9511,9 +9469,8 @@
       <c r="K40" s="9" t="s">
         <v>1652</v>
       </c>
-      <c r="L40" s="9"/>
-    </row>
-    <row r="41" spans="1:12" s="9" customFormat="1" ht="15">
+    </row>
+    <row r="41" spans="1:11" s="9" customFormat="1" ht="15">
       <c r="A41" s="9">
         <v>24010054</v>
       </c>
@@ -9547,11 +9504,8 @@
       <c r="K41" s="9" t="s">
         <v>1982</v>
       </c>
-      <c r="L41" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="9">
         <v>24010055</v>
       </c>
@@ -9585,9 +9539,8 @@
       <c r="K42" s="9" t="s">
         <v>1024</v>
       </c>
-      <c r="L42" s="9"/>
-    </row>
-    <row r="43" spans="1:12" s="10" customFormat="1">
+    </row>
+    <row r="43" spans="1:11" s="10" customFormat="1">
       <c r="A43" s="9">
         <v>24010056</v>
       </c>
@@ -9621,11 +9574,8 @@
       <c r="K43" s="9" t="s">
         <v>2048</v>
       </c>
-      <c r="L43" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="9">
         <v>24010057</v>
       </c>
@@ -9660,7 +9610,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:11">
       <c r="A45" s="9">
         <v>24010058</v>
       </c>
@@ -9694,9 +9644,8 @@
       <c r="K45" s="9" t="s">
         <v>1504</v>
       </c>
-      <c r="L45" s="9"/>
-    </row>
-    <row r="46" spans="1:12">
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="33">
         <v>24010060</v>
       </c>
@@ -9730,11 +9679,8 @@
       <c r="K46" s="33" t="s">
         <v>1767</v>
       </c>
-      <c r="L46" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="9">
         <v>24010061</v>
       </c>
@@ -9768,9 +9714,8 @@
       <c r="K47" s="9" t="s">
         <v>1582</v>
       </c>
-      <c r="L47" s="9"/>
-    </row>
-    <row r="48" spans="1:12">
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="9">
         <v>24010062</v>
       </c>
@@ -9805,7 +9750,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:11">
       <c r="A49" s="9">
         <v>24010064</v>
       </c>
@@ -9839,9 +9784,8 @@
       <c r="K49" s="9" t="s">
         <v>1600</v>
       </c>
-      <c r="L49" s="9"/>
-    </row>
-    <row r="50" spans="1:12">
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="9">
         <v>24010065</v>
       </c>
@@ -9876,7 +9820,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:11">
       <c r="A51" s="9">
         <v>24010068</v>
       </c>
@@ -9910,11 +9854,8 @@
       <c r="K51" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="L51" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="9">
         <v>24010069</v>
       </c>
@@ -9949,7 +9890,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:11">
       <c r="A53" s="9">
         <v>24010070</v>
       </c>
@@ -9984,7 +9925,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:11">
       <c r="A54" s="9">
         <v>24010071</v>
       </c>
@@ -10018,9 +9959,8 @@
       <c r="K54" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L54" s="9"/>
-    </row>
-    <row r="55" spans="1:12">
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="9">
         <v>24010073</v>
       </c>
@@ -10055,7 +9995,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:11">
       <c r="A56" s="9">
         <v>24010074</v>
       </c>
@@ -10090,7 +10030,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:11">
       <c r="A57" s="9">
         <v>24010075</v>
       </c>
@@ -10124,9 +10064,8 @@
       <c r="K57" s="13" t="s">
         <v>806</v>
       </c>
-      <c r="L57" s="10"/>
-    </row>
-    <row r="58" spans="1:12">
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="9">
         <v>24010076</v>
       </c>
@@ -10161,7 +10100,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:11">
       <c r="A59" s="9">
         <v>24010077</v>
       </c>
@@ -10196,7 +10135,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:11">
       <c r="A60" s="9">
         <v>24010079</v>
       </c>
@@ -10231,7 +10170,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:11">
       <c r="A61" s="33">
         <v>24010080</v>
       </c>
@@ -10265,9 +10204,8 @@
       <c r="K61" s="33" t="s">
         <v>1024</v>
       </c>
-      <c r="L61" s="33"/>
-    </row>
-    <row r="62" spans="1:12">
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" s="9">
         <v>24010081</v>
       </c>
@@ -10302,7 +10240,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:11">
       <c r="A63" s="9">
         <v>24010082</v>
       </c>
@@ -10336,9 +10274,8 @@
       <c r="K63" t="s">
         <v>1267</v>
       </c>
-      <c r="L63" s="9"/>
-    </row>
-    <row r="64" spans="1:12">
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" s="9">
         <v>24010084</v>
       </c>
@@ -10373,7 +10310,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:11">
       <c r="A65" s="9">
         <v>24010085</v>
       </c>
@@ -10408,7 +10345,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:11">
       <c r="A66" s="9">
         <v>24010086</v>
       </c>
@@ -10443,7 +10380,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:11">
       <c r="A67" s="9">
         <v>24010087</v>
       </c>
@@ -10477,11 +10414,8 @@
       <c r="K67" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L67" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12">
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" s="51">
         <v>24010089</v>
       </c>
@@ -10515,11 +10449,8 @@
       <c r="K68" s="51" t="s">
         <v>1790</v>
       </c>
-      <c r="L68" s="51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12">
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="9">
         <v>24010093</v>
       </c>
@@ -10553,9 +10484,8 @@
       <c r="K69" s="9" t="s">
         <v>1504</v>
       </c>
-      <c r="L69" s="9"/>
-    </row>
-    <row r="70" spans="1:12">
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="9">
         <v>24010094</v>
       </c>
@@ -10589,9 +10519,8 @@
       <c r="K70" s="9" t="s">
         <v>1431</v>
       </c>
-      <c r="L70" s="9"/>
-    </row>
-    <row r="71" spans="1:12">
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" s="9">
         <v>24010095</v>
       </c>
@@ -10625,9 +10554,8 @@
       <c r="K71" s="9" t="s">
         <v>1629</v>
       </c>
-      <c r="L71" s="9"/>
-    </row>
-    <row r="72" spans="1:12">
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" s="33">
         <v>24010096</v>
       </c>
@@ -10661,9 +10589,8 @@
       <c r="K72" s="37" t="s">
         <v>1471</v>
       </c>
-      <c r="L72" s="33"/>
-    </row>
-    <row r="73" spans="1:12">
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="9">
         <v>24010097</v>
       </c>
@@ -10697,9 +10624,8 @@
       <c r="K73" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L73" s="9"/>
-    </row>
-    <row r="74" spans="1:12">
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="9">
         <v>24010099</v>
       </c>
@@ -10733,11 +10659,8 @@
       <c r="K74" s="9" t="s">
         <v>1504</v>
       </c>
-      <c r="L74" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12">
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" s="9">
         <v>24010100</v>
       </c>
@@ -10771,9 +10694,8 @@
       <c r="K75" s="9" t="s">
         <v>1289</v>
       </c>
-      <c r="L75" s="9"/>
-    </row>
-    <row r="76" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="76" spans="1:11" s="4" customFormat="1">
       <c r="A76" s="9">
         <v>24010101</v>
       </c>
@@ -10807,9 +10729,8 @@
       <c r="K76" s="9" t="s">
         <v>1213</v>
       </c>
-      <c r="L76" s="9"/>
-    </row>
-    <row r="77" spans="1:12">
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="35">
         <v>24010102</v>
       </c>
@@ -10843,9 +10764,8 @@
       <c r="K77" s="9" t="s">
         <v>1442</v>
       </c>
-      <c r="L77" s="35"/>
-    </row>
-    <row r="78" spans="1:12">
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="33">
         <v>24010103</v>
       </c>
@@ -10879,9 +10799,8 @@
       <c r="K78" s="33" t="s">
         <v>1525</v>
       </c>
-      <c r="L78" s="33"/>
-    </row>
-    <row r="79" spans="1:12">
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="9">
         <v>24010106</v>
       </c>
@@ -10916,7 +10835,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:11">
       <c r="A80" s="9">
         <v>24010107</v>
       </c>
@@ -10950,11 +10869,8 @@
       <c r="K80" s="9" t="s">
         <v>1815</v>
       </c>
-      <c r="L80" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="81" spans="1:11" s="4" customFormat="1">
       <c r="A81" s="9">
         <v>24010108</v>
       </c>
@@ -10988,9 +10904,8 @@
       <c r="K81" s="6" t="s">
         <v>808</v>
       </c>
-      <c r="L81"/>
-    </row>
-    <row r="82" spans="1:12">
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" s="9">
         <v>24010109</v>
       </c>
@@ -11024,9 +10939,8 @@
       <c r="K82" s="9" t="s">
         <v>1696</v>
       </c>
-      <c r="L82" s="9"/>
-    </row>
-    <row r="83" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="83" spans="1:11" s="4" customFormat="1">
       <c r="A83" s="9">
         <v>24010110</v>
       </c>
@@ -11060,9 +10974,8 @@
       <c r="K83" t="s">
         <v>748</v>
       </c>
-      <c r="L83"/>
-    </row>
-    <row r="84" spans="1:12">
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84" s="9">
         <v>24010111</v>
       </c>
@@ -11096,9 +11009,8 @@
       <c r="K84" s="9" t="s">
         <v>1614</v>
       </c>
-      <c r="L84" s="9"/>
-    </row>
-    <row r="85" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="85" spans="1:11" s="4" customFormat="1">
       <c r="A85" s="9">
         <v>24010112</v>
       </c>
@@ -11132,9 +11044,8 @@
       <c r="K85" t="s">
         <v>724</v>
       </c>
-      <c r="L85"/>
-    </row>
-    <row r="86" spans="1:12">
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86" s="9">
         <v>24010113</v>
       </c>
@@ -11168,9 +11079,8 @@
       <c r="K86" s="9" t="s">
         <v>1619</v>
       </c>
-      <c r="L86" s="9"/>
-    </row>
-    <row r="87" spans="1:12">
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" s="9">
         <v>24010114</v>
       </c>
@@ -11205,7 +11115,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:11">
       <c r="A88" s="9">
         <v>24010115</v>
       </c>
@@ -11240,7 +11150,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15">
+    <row r="89" spans="1:11" ht="15">
       <c r="A89" s="9">
         <v>24010117</v>
       </c>
@@ -11274,9 +11184,8 @@
       <c r="K89" s="9" t="s">
         <v>1663</v>
       </c>
-      <c r="L89" s="9"/>
-    </row>
-    <row r="90" spans="1:12">
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" s="9">
         <v>24010118</v>
       </c>
@@ -11308,7 +11217,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:11">
       <c r="A91" s="9">
         <v>24010119</v>
       </c>
@@ -11342,9 +11251,8 @@
       <c r="K91" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L91" s="9"/>
-    </row>
-    <row r="92" spans="1:12">
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92" s="9">
         <v>24010121</v>
       </c>
@@ -11378,11 +11286,8 @@
       <c r="K92" s="9" t="s">
         <v>1024</v>
       </c>
-      <c r="L92" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="93" spans="1:11" s="4" customFormat="1">
       <c r="A93" s="9">
         <v>24010122</v>
       </c>
@@ -11416,11 +11321,8 @@
       <c r="K93" s="9" t="s">
         <v>1024</v>
       </c>
-      <c r="L93" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12">
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" s="9">
         <v>24010123</v>
       </c>
@@ -11455,7 +11357,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="4" customFormat="1">
+    <row r="95" spans="1:11" s="4" customFormat="1">
       <c r="A95" s="9">
         <v>24010124</v>
       </c>
@@ -11489,9 +11391,8 @@
       <c r="K95" s="9" t="s">
         <v>1711</v>
       </c>
-      <c r="L95" s="9"/>
-    </row>
-    <row r="96" spans="1:12">
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96" s="9">
         <v>24010125</v>
       </c>
@@ -11525,9 +11426,8 @@
       <c r="K96" s="9" t="s">
         <v>1216</v>
       </c>
-      <c r="L96" s="9"/>
-    </row>
-    <row r="97" spans="1:12">
+    </row>
+    <row r="97" spans="1:11">
       <c r="A97" s="9">
         <v>24010126</v>
       </c>
@@ -11562,7 +11462,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:11">
       <c r="A98" s="9">
         <v>24010129</v>
       </c>
@@ -11596,11 +11496,8 @@
       <c r="K98" s="9" t="s">
         <v>1783</v>
       </c>
-      <c r="L98" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="99" spans="1:11" s="4" customFormat="1">
       <c r="A99" s="9">
         <v>24010131</v>
       </c>
@@ -11634,9 +11531,8 @@
       <c r="K99" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="L99"/>
-    </row>
-    <row r="100" spans="1:12">
+    </row>
+    <row r="100" spans="1:11">
       <c r="A100" s="9">
         <v>24010133</v>
       </c>
@@ -11664,11 +11560,8 @@
         <v>3</v>
       </c>
       <c r="K100" s="9"/>
-      <c r="L100" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12">
+    </row>
+    <row r="101" spans="1:11">
       <c r="A101" s="9">
         <v>24010134</v>
       </c>
@@ -11702,9 +11595,8 @@
       <c r="K101" s="9" t="s">
         <v>1690</v>
       </c>
-      <c r="L101" s="9"/>
-    </row>
-    <row r="102" spans="1:12">
+    </row>
+    <row r="102" spans="1:11">
       <c r="A102" s="9">
         <v>24010135</v>
       </c>
@@ -11738,9 +11630,8 @@
       <c r="K102" s="13" t="s">
         <v>785</v>
       </c>
-      <c r="L102" s="10"/>
-    </row>
-    <row r="103" spans="1:12" ht="15">
+    </row>
+    <row r="103" spans="1:11" ht="15">
       <c r="A103" s="9">
         <v>24010136</v>
       </c>
@@ -11774,11 +11665,8 @@
       <c r="K103" s="9" t="s">
         <v>1746</v>
       </c>
-      <c r="L103" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12">
+    </row>
+    <row r="104" spans="1:11">
       <c r="A104" s="9">
         <v>24010137</v>
       </c>
@@ -11812,11 +11700,8 @@
       <c r="K104" s="9" t="s">
         <v>1351</v>
       </c>
-      <c r="L104" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12">
+    </row>
+    <row r="105" spans="1:11">
       <c r="A105" s="9">
         <v>24010138</v>
       </c>
@@ -11850,9 +11735,8 @@
       <c r="K105" s="9" t="s">
         <v>1294</v>
       </c>
-      <c r="L105" s="9"/>
-    </row>
-    <row r="106" spans="1:12">
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106" s="9">
         <v>24010139</v>
       </c>
@@ -11886,11 +11770,8 @@
       <c r="K106" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L106" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" s="15" customFormat="1">
+    </row>
+    <row r="107" spans="1:11" s="15" customFormat="1">
       <c r="A107" s="9">
         <v>24010141</v>
       </c>
@@ -11924,9 +11805,8 @@
       <c r="K107" s="9" t="s">
         <v>1634</v>
       </c>
-      <c r="L107" s="9"/>
-    </row>
-    <row r="108" spans="1:12">
+    </row>
+    <row r="108" spans="1:11">
       <c r="A108" s="9">
         <v>24020001</v>
       </c>
@@ -11955,7 +11835,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="109" spans="1:12" s="4" customFormat="1">
+    <row r="109" spans="1:11" s="4" customFormat="1">
       <c r="A109" s="9">
         <v>24020003</v>
       </c>
@@ -11989,9 +11869,8 @@
       <c r="K109" s="9" t="s">
         <v>1667</v>
       </c>
-      <c r="L109" s="9"/>
-    </row>
-    <row r="110" spans="1:12">
+    </row>
+    <row r="110" spans="1:11">
       <c r="A110" s="9">
         <v>24020006</v>
       </c>
@@ -12023,7 +11902,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:11">
       <c r="A111" s="9">
         <v>24020007</v>
       </c>
@@ -12058,7 +11937,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="112" spans="1:12" s="4" customFormat="1">
+    <row r="112" spans="1:11" s="4" customFormat="1">
       <c r="A112" s="9">
         <v>24020008</v>
       </c>
@@ -12092,9 +11971,8 @@
       <c r="K112" t="s">
         <v>829</v>
       </c>
-      <c r="L112"/>
-    </row>
-    <row r="113" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="113" spans="1:11" s="4" customFormat="1">
       <c r="A113" s="9">
         <v>24020010</v>
       </c>
@@ -12128,11 +12006,8 @@
       <c r="K113" s="9" t="s">
         <v>2114</v>
       </c>
-      <c r="L113" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="114" spans="1:11" s="4" customFormat="1">
       <c r="A114" s="9">
         <v>24020011</v>
       </c>
@@ -12160,9 +12035,8 @@
         <v>3</v>
       </c>
       <c r="K114"/>
-      <c r="L114"/>
-    </row>
-    <row r="115" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="115" spans="1:11" s="4" customFormat="1">
       <c r="A115" s="9">
         <v>24020012</v>
       </c>
@@ -12188,9 +12062,8 @@
         <v>3</v>
       </c>
       <c r="K115"/>
-      <c r="L115"/>
-    </row>
-    <row r="116" spans="1:12">
+    </row>
+    <row r="116" spans="1:11">
       <c r="A116" s="9">
         <v>24020013</v>
       </c>
@@ -12219,7 +12092,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:11">
       <c r="A117" s="9">
         <v>24020014</v>
       </c>
@@ -12253,11 +12126,8 @@
       <c r="K117" s="9" t="s">
         <v>1794</v>
       </c>
-      <c r="L117" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" s="4" customFormat="1" ht="13.5" customHeight="1">
+    </row>
+    <row r="118" spans="1:11" s="4" customFormat="1" ht="13.5" customHeight="1">
       <c r="A118" s="51">
         <v>24020016</v>
       </c>
@@ -12289,11 +12159,8 @@
       <c r="K118" s="51" t="s">
         <v>1802</v>
       </c>
-      <c r="L118" s="51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="119" spans="1:11" s="4" customFormat="1">
       <c r="A119" s="9">
         <v>24020017</v>
       </c>
@@ -12319,9 +12186,8 @@
         <v>3</v>
       </c>
       <c r="K119"/>
-      <c r="L119"/>
-    </row>
-    <row r="120" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="120" spans="1:11" s="4" customFormat="1">
       <c r="A120" s="9">
         <v>24020018</v>
       </c>
@@ -12353,9 +12219,8 @@
       <c r="K120" t="s">
         <v>813</v>
       </c>
-      <c r="L120"/>
-    </row>
-    <row r="121" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="121" spans="1:11" s="4" customFormat="1">
       <c r="A121" s="9">
         <v>24020019</v>
       </c>
@@ -12389,11 +12254,8 @@
       <c r="K121" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L121" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12">
+    </row>
+    <row r="122" spans="1:11">
       <c r="A122" s="9">
         <v>24020022</v>
       </c>
@@ -12428,7 +12290,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:11">
       <c r="A123" s="9">
         <v>24020023</v>
       </c>
@@ -12463,7 +12325,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="124" spans="1:12" s="4" customFormat="1">
+    <row r="124" spans="1:11" s="4" customFormat="1">
       <c r="A124" s="9">
         <v>24020025</v>
       </c>
@@ -12497,11 +12359,8 @@
       <c r="K124" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L124" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="125" spans="1:11" s="4" customFormat="1">
       <c r="A125" s="9">
         <v>24020027</v>
       </c>
@@ -12535,11 +12394,8 @@
       <c r="K125" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L125" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12">
+    </row>
+    <row r="126" spans="1:11">
       <c r="A126" s="9">
         <v>24020028</v>
       </c>
@@ -12573,9 +12429,8 @@
       <c r="K126" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L126" s="9"/>
-    </row>
-    <row r="127" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="127" spans="1:11" s="4" customFormat="1">
       <c r="A127" s="9">
         <v>24020029</v>
       </c>
@@ -12609,11 +12464,8 @@
       <c r="K127" s="9" t="s">
         <v>1802</v>
       </c>
-      <c r="L127" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="128" spans="1:11" s="4" customFormat="1">
       <c r="A128" s="9">
         <v>24020030</v>
       </c>
@@ -12647,9 +12499,8 @@
       <c r="K128" t="s">
         <v>813</v>
       </c>
-      <c r="L128"/>
-    </row>
-    <row r="129" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="129" spans="1:11" s="4" customFormat="1">
       <c r="A129" s="9">
         <v>24020032</v>
       </c>
@@ -12681,9 +12532,8 @@
       <c r="K129" t="s">
         <v>840</v>
       </c>
-      <c r="L129"/>
-    </row>
-    <row r="130" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="130" spans="1:11" s="4" customFormat="1">
       <c r="A130" s="9">
         <v>24020034</v>
       </c>
@@ -12717,9 +12567,8 @@
       <c r="K130" t="s">
         <v>817</v>
       </c>
-      <c r="L130"/>
-    </row>
-    <row r="131" spans="1:12" s="4" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="131" spans="1:11" s="4" customFormat="1" ht="15" customHeight="1">
       <c r="A131" s="9">
         <v>24020036</v>
       </c>
@@ -12753,9 +12602,8 @@
       <c r="K131" t="s">
         <v>817</v>
       </c>
-      <c r="L131"/>
-    </row>
-    <row r="132" spans="1:12" s="14" customFormat="1">
+    </row>
+    <row r="132" spans="1:11" s="14" customFormat="1">
       <c r="A132" s="9">
         <v>24020037</v>
       </c>
@@ -12789,9 +12637,8 @@
       <c r="K132" s="9" t="s">
         <v>1667</v>
       </c>
-      <c r="L132" s="9"/>
-    </row>
-    <row r="133" spans="1:12">
+    </row>
+    <row r="133" spans="1:11">
       <c r="A133" s="9">
         <v>24020038</v>
       </c>
@@ -12825,11 +12672,8 @@
       <c r="K133" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L133" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" s="4" customFormat="1" ht="17.100000000000001" customHeight="1">
+    </row>
+    <row r="134" spans="1:11" s="4" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A134" s="9">
         <v>24020040</v>
       </c>
@@ -12863,11 +12707,8 @@
       <c r="K134" s="9" t="s">
         <v>1737</v>
       </c>
-      <c r="L134" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="135" spans="1:11" s="4" customFormat="1">
       <c r="A135" s="9">
         <v>24020041</v>
       </c>
@@ -12901,11 +12742,8 @@
       <c r="K135" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L135" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="136" spans="1:11" s="4" customFormat="1">
       <c r="A136" s="9">
         <v>24020042</v>
       </c>
@@ -12933,9 +12771,8 @@
         <v>2</v>
       </c>
       <c r="K136" s="9"/>
-      <c r="L136" s="9"/>
-    </row>
-    <row r="137" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="137" spans="1:11" s="4" customFormat="1">
       <c r="A137" s="9">
         <v>24020044</v>
       </c>
@@ -12969,9 +12806,8 @@
       <c r="K137" t="s">
         <v>813</v>
       </c>
-      <c r="L137"/>
-    </row>
-    <row r="138" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="138" spans="1:11" s="4" customFormat="1">
       <c r="A138" s="9">
         <v>24020045</v>
       </c>
@@ -13005,11 +12841,8 @@
       <c r="K138" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L138" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="139" spans="1:11" s="4" customFormat="1">
       <c r="A139" s="9">
         <v>24020047</v>
       </c>
@@ -13043,9 +12876,8 @@
       <c r="K139" t="s">
         <v>813</v>
       </c>
-      <c r="L139"/>
-    </row>
-    <row r="140" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="140" spans="1:11" s="4" customFormat="1">
       <c r="A140" s="9">
         <v>24020049</v>
       </c>
@@ -13079,11 +12911,8 @@
       <c r="K140" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L140" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="141" spans="1:11" s="4" customFormat="1">
       <c r="A141" s="9">
         <v>24020052</v>
       </c>
@@ -13117,9 +12946,8 @@
       <c r="K141" t="s">
         <v>813</v>
       </c>
-      <c r="L141"/>
-    </row>
-    <row r="142" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="142" spans="1:11" s="4" customFormat="1">
       <c r="A142" s="9">
         <v>24020053</v>
       </c>
@@ -13153,11 +12981,8 @@
       <c r="K142" s="9" t="s">
         <v>1880</v>
       </c>
-      <c r="L142" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="143" spans="1:11" s="4" customFormat="1">
       <c r="A143" s="9">
         <v>24020054</v>
       </c>
@@ -13191,9 +13016,8 @@
       <c r="K143" s="6" t="s">
         <v>814</v>
       </c>
-      <c r="L143"/>
-    </row>
-    <row r="144" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="144" spans="1:11" s="4" customFormat="1">
       <c r="A144" s="9">
         <v>24020055</v>
       </c>
@@ -13225,11 +13049,8 @@
       <c r="K144" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L144" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="145" spans="1:11" s="4" customFormat="1">
       <c r="A145" s="9">
         <v>24020056</v>
       </c>
@@ -13263,11 +13084,8 @@
       <c r="K145" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L145" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="146" spans="1:11" s="4" customFormat="1">
       <c r="A146" s="9">
         <v>24020058</v>
       </c>
@@ -13299,11 +13117,8 @@
       <c r="K146" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L146" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="147" spans="1:11" s="4" customFormat="1">
       <c r="A147" s="9">
         <v>24020059</v>
       </c>
@@ -13337,11 +13152,8 @@
       <c r="K147" s="9" t="s">
         <v>813</v>
       </c>
-      <c r="L147" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="148" spans="1:11" s="4" customFormat="1">
       <c r="A148" s="9">
         <v>24020063</v>
       </c>
@@ -13373,9 +13185,8 @@
       <c r="K148" s="6" t="s">
         <v>858</v>
       </c>
-      <c r="L148"/>
-    </row>
-    <row r="149" spans="1:12" s="16" customFormat="1" ht="20.100000000000001" customHeight="1">
+    </row>
+    <row r="149" spans="1:11" s="16" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A149" s="9">
         <v>24030001</v>
       </c>
@@ -13403,9 +13214,8 @@
         <v>3</v>
       </c>
       <c r="K149"/>
-      <c r="L149"/>
-    </row>
-    <row r="150" spans="1:12">
+    </row>
+    <row r="150" spans="1:11">
       <c r="A150" s="9">
         <v>24030002</v>
       </c>
@@ -13431,7 +13241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="14.4">
+    <row r="151" spans="1:11" ht="14.4">
       <c r="A151" s="9">
         <v>24030003</v>
       </c>
@@ -13460,7 +13270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:11">
       <c r="A152" s="9">
         <v>24030004</v>
       </c>
@@ -13486,9 +13296,8 @@
         <v>3</v>
       </c>
       <c r="K152" s="9"/>
-      <c r="L152" s="9"/>
-    </row>
-    <row r="153" spans="1:12">
+    </row>
+    <row r="153" spans="1:11">
       <c r="A153" s="9">
         <v>24030005</v>
       </c>
@@ -13514,9 +13323,8 @@
         <v>3</v>
       </c>
       <c r="K153" s="9"/>
-      <c r="L153" s="9"/>
-    </row>
-    <row r="154" spans="1:12">
+    </row>
+    <row r="154" spans="1:11">
       <c r="A154" s="9">
         <v>24030006</v>
       </c>
@@ -13550,9 +13358,8 @@
       <c r="K154" s="9" t="s">
         <v>1512</v>
       </c>
-      <c r="L154" s="9"/>
-    </row>
-    <row r="155" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="155" spans="1:11" s="9" customFormat="1">
       <c r="A155" s="9">
         <v>24030007</v>
       </c>
@@ -13578,7 +13385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:11">
       <c r="A156" s="9">
         <v>24030008</v>
       </c>
@@ -13604,7 +13411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:12">
+    <row r="157" spans="1:11">
       <c r="A157" s="9">
         <v>24030009</v>
       </c>
@@ -13632,11 +13439,8 @@
         <v>2</v>
       </c>
       <c r="K157" s="9"/>
-      <c r="L157" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12">
+    </row>
+    <row r="158" spans="1:11">
       <c r="A158" s="9">
         <v>24030010</v>
       </c>
@@ -13662,7 +13466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:12">
+    <row r="159" spans="1:11">
       <c r="A159" s="9">
         <v>24030011</v>
       </c>
@@ -13688,11 +13492,8 @@
         <v>3</v>
       </c>
       <c r="K159" s="9"/>
-      <c r="L159" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12">
+    </row>
+    <row r="160" spans="1:11">
       <c r="A160" s="9">
         <v>24030012</v>
       </c>
@@ -13721,7 +13522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:12">
+    <row r="161" spans="1:11">
       <c r="A161" s="9">
         <v>24030013</v>
       </c>
@@ -13756,7 +13557,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="162" spans="1:12">
+    <row r="162" spans="1:11">
       <c r="A162" s="9">
         <v>24030014</v>
       </c>
@@ -13779,7 +13580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
+    <row r="163" spans="1:11">
       <c r="A163" s="9">
         <v>24030016</v>
       </c>
@@ -13805,11 +13606,8 @@
         <v>3</v>
       </c>
       <c r="K163" s="9"/>
-      <c r="L163" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12">
+    </row>
+    <row r="164" spans="1:11">
       <c r="A164" s="52">
         <v>24030017</v>
       </c>
@@ -13843,11 +13641,8 @@
       <c r="K164" s="52" t="s">
         <v>1905</v>
       </c>
-      <c r="L164" s="52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" ht="18.3" customHeight="1">
+    </row>
+    <row r="165" spans="1:11" ht="18.3" customHeight="1">
       <c r="A165" s="9">
         <v>24030018</v>
       </c>
@@ -13873,9 +13668,8 @@
         <v>2</v>
       </c>
       <c r="K165" s="9"/>
-      <c r="L165" s="9"/>
-    </row>
-    <row r="166" spans="1:12">
+    </row>
+    <row r="166" spans="1:11">
       <c r="A166" s="9">
         <v>24030019</v>
       </c>
@@ -13898,7 +13692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:12">
+    <row r="167" spans="1:11">
       <c r="A167" s="9">
         <v>24030020</v>
       </c>
@@ -13924,9 +13718,8 @@
         <v>2</v>
       </c>
       <c r="K167" s="9"/>
-      <c r="L167" s="9"/>
-    </row>
-    <row r="168" spans="1:12">
+    </row>
+    <row r="168" spans="1:11">
       <c r="A168" s="9">
         <v>24030021</v>
       </c>
@@ -13952,7 +13745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:12">
+    <row r="169" spans="1:11">
       <c r="A169" s="9">
         <v>24030022</v>
       </c>
@@ -13978,7 +13771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:12">
+    <row r="170" spans="1:11">
       <c r="A170" s="9">
         <v>24030023</v>
       </c>
@@ -14001,7 +13794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:12">
+    <row r="171" spans="1:11">
       <c r="A171" s="9">
         <v>24030024</v>
       </c>
@@ -14027,7 +13820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:12">
+    <row r="172" spans="1:11">
       <c r="A172" s="9">
         <v>24030025</v>
       </c>
@@ -14053,11 +13846,8 @@
         <v>3</v>
       </c>
       <c r="K172" s="9"/>
-      <c r="L172" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12">
+    </row>
+    <row r="173" spans="1:11">
       <c r="A173" s="9">
         <v>24030026</v>
       </c>
@@ -14086,7 +13876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:12">
+    <row r="174" spans="1:11">
       <c r="A174" s="9">
         <v>24030027</v>
       </c>
@@ -14112,9 +13902,8 @@
         <v>3</v>
       </c>
       <c r="K174" s="9"/>
-      <c r="L174" s="9"/>
-    </row>
-    <row r="175" spans="1:12">
+    </row>
+    <row r="175" spans="1:11">
       <c r="A175" s="9">
         <v>24030028</v>
       </c>
@@ -14143,7 +13932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:12">
+    <row r="176" spans="1:11">
       <c r="A176" s="9">
         <v>24030029</v>
       </c>
@@ -14169,9 +13958,8 @@
         <v>3</v>
       </c>
       <c r="K176" s="9"/>
-      <c r="L176" s="9"/>
-    </row>
-    <row r="177" spans="1:12">
+    </row>
+    <row r="177" spans="1:11">
       <c r="A177" s="9">
         <v>24030030</v>
       </c>
@@ -14197,9 +13985,8 @@
         <v>3</v>
       </c>
       <c r="K177" s="9"/>
-      <c r="L177" s="9"/>
-    </row>
-    <row r="178" spans="1:12">
+    </row>
+    <row r="178" spans="1:11">
       <c r="A178" s="9">
         <v>24030031</v>
       </c>
@@ -14225,7 +14012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:12">
+    <row r="179" spans="1:11">
       <c r="A179" s="9">
         <v>24030032</v>
       </c>
@@ -14259,11 +14046,8 @@
       <c r="K179" s="9" t="s">
         <v>1750</v>
       </c>
-      <c r="L179" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="180" spans="1:11" s="9" customFormat="1">
       <c r="A180" s="9">
         <v>24030033</v>
       </c>
@@ -14286,7 +14070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:12">
+    <row r="181" spans="1:11">
       <c r="A181" s="9">
         <v>24030036</v>
       </c>
@@ -14314,9 +14098,8 @@
         <v>3</v>
       </c>
       <c r="K181" s="9"/>
-      <c r="L181" s="9"/>
-    </row>
-    <row r="182" spans="1:12">
+    </row>
+    <row r="182" spans="1:11">
       <c r="A182" s="9">
         <v>24030038</v>
       </c>
@@ -14340,7 +14123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:12">
+    <row r="183" spans="1:11">
       <c r="A183" s="9">
         <v>24030039</v>
       </c>
@@ -14363,7 +14146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:12">
+    <row r="184" spans="1:11">
       <c r="A184" s="9">
         <v>24030040</v>
       </c>
@@ -14386,7 +14169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:12">
+    <row r="185" spans="1:11">
       <c r="A185" s="9">
         <v>24030041</v>
       </c>
@@ -14409,7 +14192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:12" s="9" customFormat="1">
+    <row r="186" spans="1:11" s="9" customFormat="1">
       <c r="A186" s="9">
         <v>24030042</v>
       </c>
@@ -14435,7 +14218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:12">
+    <row r="187" spans="1:11">
       <c r="A187" s="9">
         <v>24030043</v>
       </c>
@@ -14467,9 +14250,8 @@
       <c r="K187" s="4" t="s">
         <v>913</v>
       </c>
-      <c r="L187" s="4"/>
-    </row>
-    <row r="188" spans="1:12">
+    </row>
+    <row r="188" spans="1:11">
       <c r="A188" s="9">
         <v>24030044</v>
       </c>
@@ -14504,7 +14286,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="189" spans="1:12" s="14" customFormat="1" ht="19.8" customHeight="1">
+    <row r="189" spans="1:11" s="14" customFormat="1" ht="19.8" customHeight="1">
       <c r="A189" s="9">
         <v>24030045</v>
       </c>
@@ -14530,9 +14312,8 @@
         <v>3</v>
       </c>
       <c r="K189"/>
-      <c r="L189"/>
-    </row>
-    <row r="190" spans="1:12">
+    </row>
+    <row r="190" spans="1:11">
       <c r="A190" s="9">
         <v>24030046</v>
       </c>
@@ -14558,9 +14339,8 @@
         <v>3</v>
       </c>
       <c r="K190" s="9"/>
-      <c r="L190" s="9"/>
-    </row>
-    <row r="191" spans="1:12">
+    </row>
+    <row r="191" spans="1:11">
       <c r="A191" s="9">
         <v>24030047</v>
       </c>
@@ -14583,7 +14363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:12">
+    <row r="192" spans="1:11">
       <c r="A192" s="9">
         <v>24030048</v>
       </c>
@@ -14617,9 +14397,8 @@
       <c r="K192" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="L192" s="9"/>
-    </row>
-    <row r="193" spans="1:12">
+    </row>
+    <row r="193" spans="1:11">
       <c r="A193" s="9">
         <v>24030049</v>
       </c>
@@ -14642,7 +14421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:12" s="4" customFormat="1">
+    <row r="194" spans="1:11" s="4" customFormat="1">
       <c r="A194" s="9">
         <v>24030050</v>
       </c>
@@ -14677,7 +14456,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="195" spans="1:12" s="14" customFormat="1">
+    <row r="195" spans="1:11" s="14" customFormat="1">
       <c r="A195" s="9">
         <v>24030051</v>
       </c>
@@ -14703,9 +14482,8 @@
         <v>3</v>
       </c>
       <c r="K195" s="9"/>
-      <c r="L195" s="9"/>
-    </row>
-    <row r="196" spans="1:12">
+    </row>
+    <row r="196" spans="1:11">
       <c r="A196" s="9">
         <v>24030052</v>
       </c>
@@ -14733,9 +14511,8 @@
         <v>2</v>
       </c>
       <c r="K196" s="4"/>
-      <c r="L196" s="4"/>
-    </row>
-    <row r="197" spans="1:12">
+    </row>
+    <row r="197" spans="1:11">
       <c r="A197" s="9">
         <v>24030053</v>
       </c>
@@ -14758,7 +14535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:12" s="4" customFormat="1">
+    <row r="198" spans="1:11" s="4" customFormat="1">
       <c r="A198" s="9">
         <v>24030054</v>
       </c>
@@ -14790,7 +14567,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="199" spans="1:12">
+    <row r="199" spans="1:11">
       <c r="A199" s="9">
         <v>24030055</v>
       </c>
@@ -14816,9 +14593,8 @@
         <v>3</v>
       </c>
       <c r="K199" s="9"/>
-      <c r="L199" s="9"/>
-    </row>
-    <row r="200" spans="1:12">
+    </row>
+    <row r="200" spans="1:11">
       <c r="A200" s="9">
         <v>24030056</v>
       </c>
@@ -14853,7 +14629,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="201" spans="1:12">
+    <row r="201" spans="1:11">
       <c r="A201" s="9">
         <v>24030057</v>
       </c>
@@ -14883,9 +14659,8 @@
         <v>2</v>
       </c>
       <c r="K201" s="4"/>
-      <c r="L201" s="4"/>
-    </row>
-    <row r="202" spans="1:12">
+    </row>
+    <row r="202" spans="1:11">
       <c r="A202" s="9">
         <v>24030058</v>
       </c>
@@ -14917,9 +14692,8 @@
       <c r="K202" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="L202" s="9"/>
-    </row>
-    <row r="203" spans="1:12">
+    </row>
+    <row r="203" spans="1:11">
       <c r="A203" s="9">
         <v>24030059</v>
       </c>
@@ -14947,9 +14721,8 @@
         <v>3</v>
       </c>
       <c r="K203" s="4"/>
-      <c r="L203" s="4"/>
-    </row>
-    <row r="204" spans="1:12">
+    </row>
+    <row r="204" spans="1:11">
       <c r="A204" s="9">
         <v>24030060</v>
       </c>
@@ -14983,9 +14756,8 @@
       <c r="K204" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="L204" s="4"/>
-    </row>
-    <row r="205" spans="1:12">
+    </row>
+    <row r="205" spans="1:11">
       <c r="A205" s="9">
         <v>24030061</v>
       </c>
@@ -15011,9 +14783,8 @@
         <v>3</v>
       </c>
       <c r="K205" s="9"/>
-      <c r="L205" s="9"/>
-    </row>
-    <row r="206" spans="1:12">
+    </row>
+    <row r="206" spans="1:11">
       <c r="A206" s="9">
         <v>24030062</v>
       </c>
@@ -15041,9 +14812,8 @@
         <v>3</v>
       </c>
       <c r="K206" s="9"/>
-      <c r="L206" s="9"/>
-    </row>
-    <row r="207" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="207" spans="1:11" s="9" customFormat="1">
       <c r="A207" s="9">
         <v>24030063</v>
       </c>
@@ -15066,7 +14836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:12" s="9" customFormat="1">
+    <row r="208" spans="1:11" s="9" customFormat="1">
       <c r="A208" s="9">
         <v>24030064</v>
       </c>
@@ -15089,7 +14859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:12">
+    <row r="209" spans="1:11">
       <c r="A209" s="9">
         <v>24030065</v>
       </c>
@@ -15112,7 +14882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:12">
+    <row r="210" spans="1:11">
       <c r="A210" s="9">
         <v>24030066</v>
       </c>
@@ -15146,9 +14916,8 @@
       <c r="K210" s="4" t="s">
         <v>908</v>
       </c>
-      <c r="L210" s="4"/>
-    </row>
-    <row r="211" spans="1:12">
+    </row>
+    <row r="211" spans="1:11">
       <c r="A211" s="9">
         <v>24030067</v>
       </c>
@@ -15182,9 +14951,8 @@
       <c r="K211" s="9" t="s">
         <v>1401</v>
       </c>
-      <c r="L211" s="9"/>
-    </row>
-    <row r="212" spans="1:12">
+    </row>
+    <row r="212" spans="1:11">
       <c r="A212" s="9">
         <v>24030068</v>
       </c>
@@ -15207,7 +14975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:12">
+    <row r="213" spans="1:11">
       <c r="A213" s="9">
         <v>24030069</v>
       </c>
@@ -15242,7 +15010,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="214" spans="1:12">
+    <row r="214" spans="1:11">
       <c r="A214" s="9">
         <v>24030070</v>
       </c>
@@ -15265,7 +15033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:12">
+    <row r="215" spans="1:11">
       <c r="A215" s="9">
         <v>24030071</v>
       </c>
@@ -15291,9 +15059,8 @@
         <v>2</v>
       </c>
       <c r="K215" s="9"/>
-      <c r="L215" s="9"/>
-    </row>
-    <row r="216" spans="1:12">
+    </row>
+    <row r="216" spans="1:11">
       <c r="A216" s="9">
         <v>24030072</v>
       </c>
@@ -15316,7 +15083,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:12">
+    <row r="217" spans="1:11">
       <c r="A217" s="9">
         <v>24030073</v>
       </c>
@@ -15339,7 +15106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:12">
+    <row r="218" spans="1:11">
       <c r="A218" s="9">
         <v>24030074</v>
       </c>
@@ -15362,7 +15129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:12">
+    <row r="219" spans="1:11">
       <c r="A219" s="9">
         <v>24030075</v>
       </c>
@@ -15385,7 +15152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:12">
+    <row r="220" spans="1:11">
       <c r="A220" s="9">
         <v>24030076</v>
       </c>
@@ -15411,9 +15178,8 @@
         <v>3</v>
       </c>
       <c r="K220" s="9"/>
-      <c r="L220" s="9"/>
-    </row>
-    <row r="221" spans="1:12">
+    </row>
+    <row r="221" spans="1:11">
       <c r="A221" s="9">
         <v>24030077</v>
       </c>
@@ -15439,9 +15205,8 @@
         <v>3</v>
       </c>
       <c r="K221" s="9"/>
-      <c r="L221" s="9"/>
-    </row>
-    <row r="222" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="222" spans="1:11" s="9" customFormat="1">
       <c r="A222" s="9">
         <v>24030078</v>
       </c>
@@ -15469,9 +15234,8 @@
         <v>3</v>
       </c>
       <c r="K222" s="4"/>
-      <c r="L222" s="4"/>
-    </row>
-    <row r="223" spans="1:12">
+    </row>
+    <row r="223" spans="1:11">
       <c r="A223" s="9">
         <v>24030079</v>
       </c>
@@ -15506,7 +15270,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="224" spans="1:12">
+    <row r="224" spans="1:11">
       <c r="A224" s="9">
         <v>24030080</v>
       </c>
@@ -15540,9 +15304,8 @@
       <c r="K224" s="9" t="s">
         <v>1351</v>
       </c>
-      <c r="L224" s="9"/>
-    </row>
-    <row r="225" spans="1:12" s="4" customFormat="1">
+    </row>
+    <row r="225" spans="1:11" s="4" customFormat="1">
       <c r="A225" s="9">
         <v>24030081</v>
       </c>
@@ -15576,9 +15339,8 @@
       <c r="K225" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="L225" s="9"/>
-    </row>
-    <row r="226" spans="1:12" ht="16.2" customHeight="1">
+    </row>
+    <row r="226" spans="1:11" ht="16.2" customHeight="1">
       <c r="A226" s="9">
         <v>24030082</v>
       </c>
@@ -15610,9 +15372,8 @@
       <c r="K226" s="4" t="s">
         <v>919</v>
       </c>
-      <c r="L226" s="4"/>
-    </row>
-    <row r="227" spans="1:12">
+    </row>
+    <row r="227" spans="1:11">
       <c r="A227" s="9">
         <v>24030083</v>
       </c>
@@ -15635,7 +15396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:12">
+    <row r="228" spans="1:11">
       <c r="A228" s="9">
         <v>24030084</v>
       </c>
@@ -15661,9 +15422,8 @@
         <v>3</v>
       </c>
       <c r="K228" s="9"/>
-      <c r="L228" s="9"/>
-    </row>
-    <row r="229" spans="1:12">
+    </row>
+    <row r="229" spans="1:11">
       <c r="A229" s="9">
         <v>24030085</v>
       </c>
@@ -15689,9 +15449,8 @@
         <v>3</v>
       </c>
       <c r="K229" s="9"/>
-      <c r="L229" s="9"/>
-    </row>
-    <row r="230" spans="1:12">
+    </row>
+    <row r="230" spans="1:11">
       <c r="A230" s="9">
         <v>24030086</v>
       </c>
@@ -15714,7 +15473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:12">
+    <row r="231" spans="1:11">
       <c r="A231" s="9">
         <v>24030087</v>
       </c>
@@ -15740,9 +15499,8 @@
         <v>3</v>
       </c>
       <c r="K231" s="9"/>
-      <c r="L231" s="9"/>
-    </row>
-    <row r="232" spans="1:12">
+    </row>
+    <row r="232" spans="1:11">
       <c r="A232" s="9">
         <v>24030088</v>
       </c>
@@ -15765,7 +15523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:12">
+    <row r="233" spans="1:11">
       <c r="A233" s="9">
         <v>24030089</v>
       </c>
@@ -15797,9 +15555,8 @@
       <c r="K233" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="L233" s="4"/>
-    </row>
-    <row r="234" spans="1:12">
+    </row>
+    <row r="234" spans="1:11">
       <c r="A234" s="9">
         <v>24030090</v>
       </c>
@@ -15822,7 +15579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:12">
+    <row r="235" spans="1:11">
       <c r="A235" s="9">
         <v>24030091</v>
       </c>
@@ -15845,7 +15602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:12">
+    <row r="236" spans="1:11">
       <c r="A236" s="34">
         <v>24030092</v>
       </c>
@@ -15877,9 +15634,8 @@
       <c r="K236" s="34" t="s">
         <v>1392</v>
       </c>
-      <c r="L236" s="34"/>
-    </row>
-    <row r="237" spans="1:12">
+    </row>
+    <row r="237" spans="1:11">
       <c r="A237" s="9">
         <v>24030093</v>
       </c>
@@ -15907,9 +15663,8 @@
         <v>3</v>
       </c>
       <c r="K237" s="9"/>
-      <c r="L237" s="9"/>
-    </row>
-    <row r="238" spans="1:12">
+    </row>
+    <row r="238" spans="1:11">
       <c r="A238" s="33">
         <v>24030095</v>
       </c>
@@ -15941,9 +15696,8 @@
       <c r="K238" s="33" t="s">
         <v>1477</v>
       </c>
-      <c r="L238" s="33"/>
-    </row>
-    <row r="239" spans="1:12" s="14" customFormat="1">
+    </row>
+    <row r="239" spans="1:11" s="14" customFormat="1">
       <c r="A239" s="9">
         <v>24030096</v>
       </c>
@@ -15969,9 +15723,8 @@
         <v>3</v>
       </c>
       <c r="K239" s="9"/>
-      <c r="L239" s="9"/>
-    </row>
-    <row r="240" spans="1:12">
+    </row>
+    <row r="240" spans="1:11">
       <c r="A240" s="9">
         <v>24030097</v>
       </c>
@@ -16000,7 +15753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:12">
+    <row r="241" spans="1:11">
       <c r="A241" s="9">
         <v>24030098</v>
       </c>
@@ -16028,11 +15781,8 @@
         <v>2</v>
       </c>
       <c r="K241" s="9"/>
-      <c r="L241" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="242" spans="1:12">
+    </row>
+    <row r="242" spans="1:11">
       <c r="A242" s="9">
         <v>24030099</v>
       </c>
@@ -16055,7 +15805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:12">
+    <row r="243" spans="1:11">
       <c r="A243" s="9">
         <v>24030100</v>
       </c>
@@ -16081,9 +15831,8 @@
         <v>3</v>
       </c>
       <c r="K243" s="9"/>
-      <c r="L243" s="9"/>
-    </row>
-    <row r="244" spans="1:12">
+    </row>
+    <row r="244" spans="1:11">
       <c r="A244" s="9">
         <v>24030101</v>
       </c>
@@ -16112,7 +15861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:12">
+    <row r="245" spans="1:11">
       <c r="A245" s="9">
         <v>24030102</v>
       </c>
@@ -16138,7 +15887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:12">
+    <row r="246" spans="1:11">
       <c r="A246" s="9">
         <v>24030103</v>
       </c>
@@ -16166,9 +15915,8 @@
         <v>3</v>
       </c>
       <c r="K246" s="9"/>
-      <c r="L246" s="9"/>
-    </row>
-    <row r="247" spans="1:12">
+    </row>
+    <row r="247" spans="1:11">
       <c r="A247" s="9">
         <v>24030104</v>
       </c>
@@ -16194,9 +15942,8 @@
         <v>3</v>
       </c>
       <c r="K247" s="9"/>
-      <c r="L247" s="9"/>
-    </row>
-    <row r="248" spans="1:12">
+    </row>
+    <row r="248" spans="1:11">
       <c r="A248" s="9">
         <v>24030105</v>
       </c>
@@ -16230,9 +15977,8 @@
       <c r="K248" s="9" t="s">
         <v>1446</v>
       </c>
-      <c r="L248" s="9"/>
-    </row>
-    <row r="249" spans="1:12">
+    </row>
+    <row r="249" spans="1:11">
       <c r="A249" s="9">
         <v>24030107</v>
       </c>
@@ -16260,9 +16006,8 @@
         <v>3</v>
       </c>
       <c r="K249" s="9"/>
-      <c r="L249" s="9"/>
-    </row>
-    <row r="250" spans="1:12">
+    </row>
+    <row r="250" spans="1:11">
       <c r="A250" s="9">
         <v>24030108</v>
       </c>
@@ -16285,7 +16030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:12">
+    <row r="251" spans="1:11">
       <c r="A251" s="9">
         <v>24030109</v>
       </c>
@@ -16311,9 +16056,8 @@
         <v>3</v>
       </c>
       <c r="K251" s="15"/>
-      <c r="L251" s="15"/>
-    </row>
-    <row r="252" spans="1:12">
+    </row>
+    <row r="252" spans="1:11">
       <c r="A252" s="9">
         <v>24030110</v>
       </c>
@@ -16339,11 +16083,8 @@
         <v>3</v>
       </c>
       <c r="K252" s="9"/>
-      <c r="L252" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="253" spans="1:12">
+    </row>
+    <row r="253" spans="1:11">
       <c r="A253" s="9">
         <v>24040001</v>
       </c>
@@ -16378,7 +16119,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="254" spans="1:12">
+    <row r="254" spans="1:11">
       <c r="A254" s="9">
         <v>24040002</v>
       </c>
@@ -16412,9 +16153,8 @@
       <c r="K254" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="L254" s="4"/>
-    </row>
-    <row r="255" spans="1:12">
+    </row>
+    <row r="255" spans="1:11">
       <c r="A255" s="9">
         <v>24040003</v>
       </c>
@@ -16449,7 +16189,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="256" spans="1:12">
+    <row r="256" spans="1:11">
       <c r="A256" s="9">
         <v>24040004</v>
       </c>
@@ -16484,7 +16224,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="257" spans="1:12">
+    <row r="257" spans="1:11">
       <c r="A257" s="9">
         <v>24040005</v>
       </c>
@@ -16518,9 +16258,8 @@
       <c r="K257" s="9" t="s">
         <v>1303</v>
       </c>
-      <c r="L257" s="9"/>
-    </row>
-    <row r="258" spans="1:12">
+    </row>
+    <row r="258" spans="1:11">
       <c r="A258" s="9">
         <v>24040006</v>
       </c>
@@ -16554,9 +16293,8 @@
       <c r="K258" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="L258" s="4"/>
-    </row>
-    <row r="259" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="259" spans="1:11" s="9" customFormat="1">
       <c r="A259" s="9">
         <v>24040007</v>
       </c>
@@ -16590,9 +16328,8 @@
       <c r="K259" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="L259" s="4"/>
-    </row>
-    <row r="260" spans="1:12">
+    </row>
+    <row r="260" spans="1:11">
       <c r="A260" s="9">
         <v>24040008</v>
       </c>
@@ -16626,11 +16363,8 @@
       <c r="K260" s="9" t="s">
         <v>1936</v>
       </c>
-      <c r="L260" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="261" spans="1:12" ht="30.6" customHeight="1">
+    </row>
+    <row r="261" spans="1:11" ht="30.6" customHeight="1">
       <c r="A261" s="9">
         <v>24040009</v>
       </c>
@@ -16664,9 +16398,8 @@
       <c r="K261" s="5" t="s">
         <v>929</v>
       </c>
-      <c r="L261" s="4"/>
-    </row>
-    <row r="262" spans="1:12">
+    </row>
+    <row r="262" spans="1:11">
       <c r="A262" s="9">
         <v>24040010</v>
       </c>
@@ -16700,9 +16433,8 @@
       <c r="K262" s="4" t="s">
         <v>964</v>
       </c>
-      <c r="L262" s="4"/>
-    </row>
-    <row r="263" spans="1:12">
+    </row>
+    <row r="263" spans="1:11">
       <c r="A263" s="9">
         <v>24040012</v>
       </c>
@@ -16734,11 +16466,8 @@
       <c r="K263" s="9" t="s">
         <v>1779</v>
       </c>
-      <c r="L263" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="264" spans="1:12">
+    </row>
+    <row r="264" spans="1:11">
       <c r="A264" s="9">
         <v>24040013</v>
       </c>
@@ -16772,9 +16501,8 @@
       <c r="K264" s="4" t="s">
         <v>965</v>
       </c>
-      <c r="L264" s="4"/>
-    </row>
-    <row r="265" spans="1:12">
+    </row>
+    <row r="265" spans="1:11">
       <c r="A265" s="9">
         <v>24040014</v>
       </c>
@@ -16809,7 +16537,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="266" spans="1:12">
+    <row r="266" spans="1:11">
       <c r="A266" s="9">
         <v>24040015</v>
       </c>
@@ -16844,7 +16572,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="267" spans="1:12" s="14" customFormat="1">
+    <row r="267" spans="1:11" s="14" customFormat="1">
       <c r="A267" s="9">
         <v>24040017</v>
       </c>
@@ -16876,11 +16604,8 @@
       <c r="K267" s="9" t="s">
         <v>1728</v>
       </c>
-      <c r="L267" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="268" spans="1:12">
+    </row>
+    <row r="268" spans="1:11">
       <c r="A268" s="9">
         <v>24040018</v>
       </c>
@@ -16914,11 +16639,8 @@
       <c r="K268" s="9" t="s">
         <v>2078</v>
       </c>
-      <c r="L268" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="269" spans="1:12">
+    </row>
+    <row r="269" spans="1:11">
       <c r="A269" s="9">
         <v>24040019</v>
       </c>
@@ -16952,9 +16674,8 @@
       <c r="K269" s="5" t="s">
         <v>966</v>
       </c>
-      <c r="L269" s="4"/>
-    </row>
-    <row r="270" spans="1:12">
+    </row>
+    <row r="270" spans="1:11">
       <c r="A270" s="9">
         <v>24040020</v>
       </c>
@@ -16988,9 +16709,8 @@
       <c r="K270" s="4" t="s">
         <v>965</v>
       </c>
-      <c r="L270" s="4"/>
-    </row>
-    <row r="271" spans="1:12">
+    </row>
+    <row r="271" spans="1:11">
       <c r="A271" s="9">
         <v>24040021</v>
       </c>
@@ -17020,9 +16740,8 @@
         <v>3</v>
       </c>
       <c r="K271" s="9"/>
-      <c r="L271" s="9"/>
-    </row>
-    <row r="272" spans="1:12" ht="15">
+    </row>
+    <row r="272" spans="1:11" ht="15">
       <c r="A272" s="9">
         <v>24040022</v>
       </c>
@@ -17056,9 +16775,8 @@
       <c r="K272" s="9" t="s">
         <v>1672</v>
       </c>
-      <c r="L272" s="9"/>
-    </row>
-    <row r="273" spans="1:12">
+    </row>
+    <row r="273" spans="1:11">
       <c r="A273" s="9">
         <v>24040023</v>
       </c>
@@ -17092,11 +16810,8 @@
       <c r="K273" s="9" t="s">
         <v>1731</v>
       </c>
-      <c r="L273" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274" spans="1:12">
+    </row>
+    <row r="274" spans="1:11">
       <c r="A274" s="9">
         <v>24040024</v>
       </c>
@@ -17128,11 +16843,8 @@
       <c r="K274" s="9" t="s">
         <v>1779</v>
       </c>
-      <c r="L274" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:12">
+    </row>
+    <row r="275" spans="1:11">
       <c r="A275" s="9">
         <v>24040026</v>
       </c>
@@ -17166,11 +16878,8 @@
       <c r="K275" s="9" t="s">
         <v>1731</v>
       </c>
-      <c r="L275" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:12">
+    </row>
+    <row r="276" spans="1:11">
       <c r="A276" s="9">
         <v>24040027</v>
       </c>
@@ -17204,9 +16913,8 @@
       <c r="K276" s="4" t="s">
         <v>967</v>
       </c>
-      <c r="L276" s="4"/>
-    </row>
-    <row r="277" spans="1:12">
+    </row>
+    <row r="277" spans="1:11">
       <c r="A277" s="9">
         <v>24040028</v>
       </c>
@@ -17240,9 +16948,8 @@
       <c r="K277" s="4" t="s">
         <v>968</v>
       </c>
-      <c r="L277" s="4"/>
-    </row>
-    <row r="278" spans="1:12">
+    </row>
+    <row r="278" spans="1:11">
       <c r="A278" s="9">
         <v>24040029</v>
       </c>
@@ -17277,7 +16984,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="279" spans="1:12">
+    <row r="279" spans="1:11">
       <c r="A279" s="9">
         <v>24040030</v>
       </c>
@@ -17311,9 +17018,8 @@
       <c r="K279" s="9" t="s">
         <v>1397</v>
       </c>
-      <c r="L279" s="9"/>
-    </row>
-    <row r="280" spans="1:12" ht="24.6" customHeight="1">
+    </row>
+    <row r="280" spans="1:11" ht="24.6" customHeight="1">
       <c r="A280" s="9">
         <v>24040031</v>
       </c>
@@ -17345,11 +17051,8 @@
       <c r="K280" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="L280" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="281" spans="1:12">
+    </row>
+    <row r="281" spans="1:11">
       <c r="A281" s="9">
         <v>24040032</v>
       </c>
@@ -17383,9 +17086,8 @@
       <c r="K281" s="9" t="s">
         <v>1537</v>
       </c>
-      <c r="L281" s="9"/>
-    </row>
-    <row r="282" spans="1:12">
+    </row>
+    <row r="282" spans="1:11">
       <c r="A282" s="9">
         <v>24040033</v>
       </c>
@@ -17420,7 +17122,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="283" spans="1:12">
+    <row r="283" spans="1:11">
       <c r="A283" s="9">
         <v>24040034</v>
       </c>
@@ -17448,9 +17150,8 @@
         <v>3</v>
       </c>
       <c r="K283" s="4"/>
-      <c r="L283" s="4"/>
-    </row>
-    <row r="284" spans="1:12">
+    </row>
+    <row r="284" spans="1:11">
       <c r="A284" s="9">
         <v>24040035</v>
       </c>
@@ -17484,9 +17185,8 @@
       <c r="K284" s="9" t="s">
         <v>1464</v>
       </c>
-      <c r="L284" s="9"/>
-    </row>
-    <row r="285" spans="1:12">
+    </row>
+    <row r="285" spans="1:11">
       <c r="A285" s="9">
         <v>24040036</v>
       </c>
@@ -17520,9 +17220,8 @@
       <c r="K285" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="L285" s="4"/>
-    </row>
-    <row r="286" spans="1:12">
+    </row>
+    <row r="286" spans="1:11">
       <c r="A286" s="9">
         <v>24040037</v>
       </c>
@@ -17557,7 +17256,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="287" spans="1:12">
+    <row r="287" spans="1:11">
       <c r="A287" s="9">
         <v>24040039</v>
       </c>
@@ -17591,11 +17290,8 @@
       <c r="K287" s="9" t="s">
         <v>1724</v>
       </c>
-      <c r="L287" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="288" spans="1:12">
+    </row>
+    <row r="288" spans="1:11">
       <c r="A288" s="9">
         <v>24040040</v>
       </c>
@@ -17623,11 +17319,8 @@
         <v>3</v>
       </c>
       <c r="K288" s="9"/>
-      <c r="L288" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:12">
+    </row>
+    <row r="289" spans="1:11">
       <c r="A289" s="9">
         <v>24040042</v>
       </c>
@@ -17661,9 +17354,8 @@
       <c r="K289" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L289" s="9"/>
-    </row>
-    <row r="290" spans="1:12">
+    </row>
+    <row r="290" spans="1:11">
       <c r="A290" s="9">
         <v>24040044</v>
       </c>
@@ -17697,11 +17389,8 @@
       <c r="K290" s="9" t="s">
         <v>2165</v>
       </c>
-      <c r="L290" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:12">
+    </row>
+    <row r="291" spans="1:11">
       <c r="A291" s="9">
         <v>24040045</v>
       </c>
@@ -17735,11 +17424,8 @@
       <c r="K291" s="9" t="s">
         <v>788</v>
       </c>
-      <c r="L291" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:12">
+    </row>
+    <row r="292" spans="1:11">
       <c r="A292" s="9">
         <v>24040046</v>
       </c>
@@ -17773,11 +17459,8 @@
       <c r="K292" s="9" t="s">
         <v>2055</v>
       </c>
-      <c r="L292" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:12">
+    </row>
+    <row r="293" spans="1:11">
       <c r="A293" s="9">
         <v>24040047</v>
       </c>
@@ -17809,9 +17492,8 @@
       <c r="K293" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="L293" s="4"/>
-    </row>
-    <row r="294" spans="1:12">
+    </row>
+    <row r="294" spans="1:11">
       <c r="A294" s="9">
         <v>24040048</v>
       </c>
@@ -17845,11 +17527,8 @@
       <c r="K294" s="9" t="s">
         <v>1756</v>
       </c>
-      <c r="L294" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295" spans="1:12" ht="15">
+    </row>
+    <row r="295" spans="1:11" ht="15">
       <c r="A295" s="9">
         <v>24040050</v>
       </c>
@@ -17883,9 +17562,8 @@
       <c r="K295" s="9" t="s">
         <v>1308</v>
       </c>
-      <c r="L295" s="9"/>
-    </row>
-    <row r="296" spans="1:12">
+    </row>
+    <row r="296" spans="1:11">
       <c r="A296" s="9">
         <v>24040051</v>
       </c>
@@ -17919,9 +17597,8 @@
       <c r="K296" s="4" t="s">
         <v>965</v>
       </c>
-      <c r="L296" s="4"/>
-    </row>
-    <row r="297" spans="1:12">
+    </row>
+    <row r="297" spans="1:11">
       <c r="A297" s="9">
         <v>24040053</v>
       </c>
@@ -17955,9 +17632,8 @@
       <c r="K297" s="9" t="s">
         <v>1610</v>
       </c>
-      <c r="L297" s="9"/>
-    </row>
-    <row r="298" spans="1:12">
+    </row>
+    <row r="298" spans="1:11">
       <c r="A298" s="9">
         <v>24040054</v>
       </c>
@@ -17991,11 +17667,8 @@
       <c r="K298" s="9" t="s">
         <v>2141</v>
       </c>
-      <c r="L298" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="299" spans="1:12">
+    </row>
+    <row r="299" spans="1:11">
       <c r="A299" s="9">
         <v>24040055</v>
       </c>
@@ -18029,9 +17702,8 @@
       <c r="K299" s="4" t="s">
         <v>969</v>
       </c>
-      <c r="L299" s="4"/>
-    </row>
-    <row r="300" spans="1:12">
+    </row>
+    <row r="300" spans="1:11">
       <c r="A300" s="9">
         <v>24040056</v>
       </c>
@@ -18065,11 +17737,8 @@
       <c r="K300" s="9" t="s">
         <v>1989</v>
       </c>
-      <c r="L300" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301" spans="1:12">
+    </row>
+    <row r="301" spans="1:11">
       <c r="A301" s="9">
         <v>24040057</v>
       </c>
@@ -18103,9 +17772,8 @@
       <c r="K301" s="4" t="s">
         <v>970</v>
       </c>
-      <c r="L301" s="4"/>
-    </row>
-    <row r="302" spans="1:12">
+    </row>
+    <row r="302" spans="1:11">
       <c r="A302" s="9">
         <v>24040059</v>
       </c>
@@ -18139,9 +17807,8 @@
       <c r="K302" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="L302" s="4"/>
-    </row>
-    <row r="303" spans="1:12">
+    </row>
+    <row r="303" spans="1:11">
       <c r="A303" s="9">
         <v>24050001</v>
       </c>
@@ -18175,9 +17842,8 @@
       <c r="K303" s="9" t="s">
         <v>1605</v>
       </c>
-      <c r="L303" s="9"/>
-    </row>
-    <row r="304" spans="1:12">
+    </row>
+    <row r="304" spans="1:11">
       <c r="A304" s="9">
         <v>24050002</v>
       </c>
@@ -18211,9 +17877,8 @@
       <c r="K304" s="9" t="s">
         <v>958</v>
       </c>
-      <c r="L304" s="9"/>
-    </row>
-    <row r="305" spans="1:12">
+    </row>
+    <row r="305" spans="1:11">
       <c r="A305" s="9">
         <v>24050006</v>
       </c>
@@ -18241,11 +17906,8 @@
         <v>3</v>
       </c>
       <c r="K305" s="9"/>
-      <c r="L305" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="306" spans="1:12">
+    </row>
+    <row r="306" spans="1:11">
       <c r="A306" s="9">
         <v>24050007</v>
       </c>
@@ -18271,11 +17933,8 @@
         <v>3</v>
       </c>
       <c r="K306" s="9"/>
-      <c r="L306" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="307" spans="1:12">
+    </row>
+    <row r="307" spans="1:11">
       <c r="A307" s="9">
         <v>24050009</v>
       </c>
@@ -18301,11 +17960,8 @@
         <v>3</v>
       </c>
       <c r="K307" s="9"/>
-      <c r="L307" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="308" spans="1:12">
+    </row>
+    <row r="308" spans="1:11">
       <c r="A308" s="9">
         <v>24050010</v>
       </c>
@@ -18331,9 +17987,8 @@
         <v>3</v>
       </c>
       <c r="K308" s="14"/>
-      <c r="L308" s="14"/>
-    </row>
-    <row r="309" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="309" spans="1:11" s="9" customFormat="1">
       <c r="A309" s="9">
         <v>24050011</v>
       </c>
@@ -18359,9 +18014,8 @@
         <v>3</v>
       </c>
       <c r="K309"/>
-      <c r="L309"/>
-    </row>
-    <row r="310" spans="1:12">
+    </row>
+    <row r="310" spans="1:11">
       <c r="A310" s="9">
         <v>24050012</v>
       </c>
@@ -18387,11 +18041,8 @@
         <v>3</v>
       </c>
       <c r="K310" s="9"/>
-      <c r="L310" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="311" spans="1:12">
+    </row>
+    <row r="311" spans="1:11">
       <c r="A311" s="9">
         <v>24050015</v>
       </c>
@@ -18414,7 +18065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:12">
+    <row r="312" spans="1:11">
       <c r="A312" s="9">
         <v>24050016</v>
       </c>
@@ -18440,9 +18091,8 @@
         <v>3</v>
       </c>
       <c r="K312" s="4"/>
-      <c r="L312" s="4"/>
-    </row>
-    <row r="313" spans="1:12">
+    </row>
+    <row r="313" spans="1:11">
       <c r="A313" s="9">
         <v>24050018</v>
       </c>
@@ -18472,9 +18122,8 @@
         <v>2</v>
       </c>
       <c r="K313" s="4"/>
-      <c r="L313" s="4"/>
-    </row>
-    <row r="314" spans="1:12">
+    </row>
+    <row r="314" spans="1:11">
       <c r="A314" s="9">
         <v>24050019</v>
       </c>
@@ -18500,11 +18149,8 @@
         <v>3</v>
       </c>
       <c r="K314" s="9"/>
-      <c r="L314" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="315" spans="1:12">
+    </row>
+    <row r="315" spans="1:11">
       <c r="A315" s="9">
         <v>24050021</v>
       </c>
@@ -18538,9 +18184,8 @@
       <c r="K315" s="4" t="s">
         <v>971</v>
       </c>
-      <c r="L315" s="4"/>
-    </row>
-    <row r="316" spans="1:12">
+    </row>
+    <row r="316" spans="1:11">
       <c r="A316" s="9">
         <v>24050022</v>
       </c>
@@ -18574,11 +18219,8 @@
       <c r="K316" s="9" t="s">
         <v>1446</v>
       </c>
-      <c r="L316" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="317" spans="1:12">
+    </row>
+    <row r="317" spans="1:11">
       <c r="A317" s="9">
         <v>24050023</v>
       </c>
@@ -18608,11 +18250,8 @@
         <v>2</v>
       </c>
       <c r="K317" s="9"/>
-      <c r="L317" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="318" spans="1:12">
+    </row>
+    <row r="318" spans="1:11">
       <c r="A318" s="9">
         <v>24050024</v>
       </c>
@@ -18644,11 +18283,8 @@
       <c r="K318" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="L318" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="319" spans="1:12">
+    </row>
+    <row r="319" spans="1:11">
       <c r="A319" s="9">
         <v>24050025</v>
       </c>
@@ -18682,9 +18318,8 @@
       <c r="K319" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="L319" s="9"/>
-    </row>
-    <row r="320" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="320" spans="1:11" s="33" customFormat="1">
       <c r="A320" s="9">
         <v>24050026</v>
       </c>
@@ -18712,11 +18347,8 @@
         <v>3</v>
       </c>
       <c r="K320" s="9"/>
-      <c r="L320" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="321" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="321" spans="1:11" s="33" customFormat="1">
       <c r="A321" s="9">
         <v>24050027</v>
       </c>
@@ -18748,11 +18380,8 @@
       <c r="K321" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="L321" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="322" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="322" spans="1:11" s="9" customFormat="1">
       <c r="A322" s="52">
         <v>24050029</v>
       </c>
@@ -18786,11 +18415,8 @@
       <c r="K322" s="52" t="s">
         <v>1809</v>
       </c>
-      <c r="L322" s="52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="323" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="323" spans="1:11" s="9" customFormat="1">
       <c r="A323" s="9">
         <v>24050031</v>
       </c>
@@ -18818,9 +18444,8 @@
         <v>3</v>
       </c>
       <c r="K323" s="4"/>
-      <c r="L323" s="4"/>
-    </row>
-    <row r="324" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="324" spans="1:11" s="9" customFormat="1">
       <c r="A324" s="9">
         <v>24050032</v>
       </c>
@@ -18845,11 +18470,8 @@
       <c r="J324" s="9">
         <v>3</v>
       </c>
-      <c r="L324" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="325" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="325" spans="1:11" s="9" customFormat="1">
       <c r="A325" s="9">
         <v>24050033</v>
       </c>
@@ -18877,9 +18499,8 @@
         <v>2</v>
       </c>
       <c r="K325" s="4"/>
-      <c r="L325" s="4"/>
-    </row>
-    <row r="326" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="326" spans="1:11" s="9" customFormat="1">
       <c r="A326" s="9">
         <v>24050036</v>
       </c>
@@ -18904,11 +18525,8 @@
       <c r="J326" s="9">
         <v>3</v>
       </c>
-      <c r="L326" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="327" spans="1:11" s="9" customFormat="1">
       <c r="A327" s="9">
         <v>24050037</v>
       </c>
@@ -18937,7 +18555,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="328" spans="1:12" s="9" customFormat="1">
+    <row r="328" spans="1:11" s="9" customFormat="1">
       <c r="A328" s="9">
         <v>24050040</v>
       </c>
@@ -18968,11 +18586,8 @@
       <c r="K328" s="9" t="s">
         <v>1854</v>
       </c>
-      <c r="L328" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="329" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="329" spans="1:11" s="33" customFormat="1">
       <c r="A329" s="9">
         <v>24050041</v>
       </c>
@@ -19006,9 +18621,8 @@
       <c r="K329" s="5" t="s">
         <v>922</v>
       </c>
-      <c r="L329" s="4"/>
-    </row>
-    <row r="330" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="330" spans="1:11" s="9" customFormat="1">
       <c r="A330" s="9">
         <v>24050042</v>
       </c>
@@ -19042,9 +18656,8 @@
       <c r="K330" s="4" t="s">
         <v>813</v>
       </c>
-      <c r="L330" s="4"/>
-    </row>
-    <row r="331" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="331" spans="1:11" s="9" customFormat="1">
       <c r="A331" s="9">
         <v>24050043</v>
       </c>
@@ -19074,9 +18687,8 @@
         <v>2</v>
       </c>
       <c r="K331" s="4"/>
-      <c r="L331" s="4"/>
-    </row>
-    <row r="332" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="332" spans="1:11" s="9" customFormat="1">
       <c r="A332" s="9">
         <v>24050044</v>
       </c>
@@ -19104,9 +18716,8 @@
         <v>2</v>
       </c>
       <c r="K332" s="4"/>
-      <c r="L332" s="4"/>
-    </row>
-    <row r="333" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="333" spans="1:11" s="9" customFormat="1">
       <c r="A333" s="9">
         <v>24050045</v>
       </c>
@@ -19134,9 +18745,8 @@
         <v>3</v>
       </c>
       <c r="K333" s="4"/>
-      <c r="L333" s="4"/>
-    </row>
-    <row r="334" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="334" spans="1:11" s="9" customFormat="1">
       <c r="A334" s="9">
         <v>24050046</v>
       </c>
@@ -19171,7 +18781,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="335" spans="1:12" s="9" customFormat="1">
+    <row r="335" spans="1:11" s="9" customFormat="1">
       <c r="A335" s="9">
         <v>24050047</v>
       </c>
@@ -19199,11 +18809,8 @@
       <c r="J335" s="9">
         <v>3</v>
       </c>
-      <c r="L335" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="336" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="336" spans="1:11" s="9" customFormat="1">
       <c r="A336" s="9">
         <v>24050052</v>
       </c>
@@ -19237,11 +18844,8 @@
       <c r="K336" s="9" t="s">
         <v>2030</v>
       </c>
-      <c r="L336" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="337" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="337" spans="1:11" s="9" customFormat="1">
       <c r="A337" s="9">
         <v>24050053</v>
       </c>
@@ -19267,7 +18871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="338" spans="1:12" s="9" customFormat="1">
+    <row r="338" spans="1:11" s="9" customFormat="1">
       <c r="A338" s="9">
         <v>24050055</v>
       </c>
@@ -19302,7 +18906,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="339" spans="1:12" s="9" customFormat="1">
+    <row r="339" spans="1:11" s="9" customFormat="1">
       <c r="A339" s="9">
         <v>24050056</v>
       </c>
@@ -19333,11 +18937,8 @@
       <c r="K339" s="9" t="s">
         <v>1940</v>
       </c>
-      <c r="L339" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="340" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="340" spans="1:11" s="9" customFormat="1">
       <c r="A340" s="9">
         <v>24050057</v>
       </c>
@@ -19368,11 +18969,8 @@
       <c r="K340" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="L340" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="341" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="341" spans="1:11" s="33" customFormat="1">
       <c r="A341" s="9">
         <v>24050058</v>
       </c>
@@ -19400,11 +18998,8 @@
         <v>3</v>
       </c>
       <c r="K341" s="9"/>
-      <c r="L341" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="342" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="342" spans="1:11" s="9" customFormat="1">
       <c r="A342" s="9">
         <v>24050059</v>
       </c>
@@ -19429,11 +19024,8 @@
       <c r="J342" s="9">
         <v>2</v>
       </c>
-      <c r="L342" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="343" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="343" spans="1:11" s="9" customFormat="1">
       <c r="A343" s="9">
         <v>24050061</v>
       </c>
@@ -19455,11 +19047,8 @@
       <c r="J343" s="9">
         <v>2</v>
       </c>
-      <c r="L343" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="344" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="344" spans="1:11" s="9" customFormat="1">
       <c r="A344" s="9">
         <v>24050062</v>
       </c>
@@ -19484,11 +19073,8 @@
       <c r="J344" s="9">
         <v>3</v>
       </c>
-      <c r="L344" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="345" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="345" spans="1:11" s="9" customFormat="1">
       <c r="A345" s="9">
         <v>24050063</v>
       </c>
@@ -19520,9 +19106,8 @@
       <c r="K345" s="4" t="s">
         <v>961</v>
       </c>
-      <c r="L345" s="4"/>
-    </row>
-    <row r="346" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="346" spans="1:11" s="9" customFormat="1">
       <c r="A346" s="9">
         <v>24050064</v>
       </c>
@@ -19556,9 +19141,8 @@
       <c r="K346" s="4" t="s">
         <v>974</v>
       </c>
-      <c r="L346" s="4"/>
-    </row>
-    <row r="347" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="347" spans="1:11" s="9" customFormat="1">
       <c r="A347" s="9">
         <v>24050066</v>
       </c>
@@ -19586,9 +19170,8 @@
         <v>3</v>
       </c>
       <c r="K347" s="4"/>
-      <c r="L347" s="4"/>
-    </row>
-    <row r="348" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="348" spans="1:11" s="9" customFormat="1">
       <c r="A348" s="9">
         <v>24050067</v>
       </c>
@@ -19616,9 +19199,8 @@
         <v>3</v>
       </c>
       <c r="K348" s="4"/>
-      <c r="L348" s="4"/>
-    </row>
-    <row r="349" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="349" spans="1:11" s="9" customFormat="1">
       <c r="A349" s="9">
         <v>24050069</v>
       </c>
@@ -19646,9 +19228,8 @@
         <v>3</v>
       </c>
       <c r="K349" s="4"/>
-      <c r="L349" s="4"/>
-    </row>
-    <row r="350" spans="1:12" s="9" customFormat="1" ht="13.2" customHeight="1">
+    </row>
+    <row r="350" spans="1:11" s="9" customFormat="1" ht="13.2" customHeight="1">
       <c r="A350" s="9">
         <v>24050070</v>
       </c>
@@ -19676,9 +19257,8 @@
         <v>3</v>
       </c>
       <c r="K350" s="16"/>
-      <c r="L350" s="16"/>
-    </row>
-    <row r="351" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="351" spans="1:11" s="9" customFormat="1">
       <c r="A351" s="9">
         <v>24050071</v>
       </c>
@@ -19700,11 +19280,8 @@
       <c r="J351" s="9">
         <v>3</v>
       </c>
-      <c r="L351" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="352" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="352" spans="1:11" s="9" customFormat="1">
       <c r="A352" s="9">
         <v>24050073</v>
       </c>
@@ -19730,9 +19307,8 @@
         <v>3</v>
       </c>
       <c r="K352"/>
-      <c r="L352"/>
-    </row>
-    <row r="353" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="353" spans="1:11" s="9" customFormat="1">
       <c r="A353" s="9">
         <v>24050074</v>
       </c>
@@ -19758,9 +19334,8 @@
         <v>3</v>
       </c>
       <c r="K353"/>
-      <c r="L353"/>
-    </row>
-    <row r="354" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="354" spans="1:11" s="9" customFormat="1">
       <c r="A354" s="9">
         <v>24050075</v>
       </c>
@@ -19794,11 +19369,8 @@
       <c r="K354" s="9" t="s">
         <v>2073</v>
       </c>
-      <c r="L354" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="355" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="355" spans="1:11" s="9" customFormat="1">
       <c r="A355" s="9">
         <v>24050076</v>
       </c>
@@ -19821,7 +19393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:12" s="9" customFormat="1">
+    <row r="356" spans="1:11" s="9" customFormat="1">
       <c r="A356" s="9">
         <v>24050077</v>
       </c>
@@ -19847,9 +19419,8 @@
         <v>3</v>
       </c>
       <c r="K356"/>
-      <c r="L356"/>
-    </row>
-    <row r="357" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="357" spans="1:11" s="9" customFormat="1">
       <c r="A357" s="9">
         <v>24050078</v>
       </c>
@@ -19871,11 +19442,8 @@
       <c r="J357" s="9">
         <v>3</v>
       </c>
-      <c r="L357" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="358" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="358" spans="1:11" s="9" customFormat="1">
       <c r="A358" s="9">
         <v>24050079</v>
       </c>
@@ -19900,11 +19468,8 @@
       <c r="J358" s="9">
         <v>3</v>
       </c>
-      <c r="L358" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="359" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="359" spans="1:11" s="9" customFormat="1">
       <c r="A359" s="9">
         <v>24050080</v>
       </c>
@@ -19930,9 +19495,8 @@
         <v>3</v>
       </c>
       <c r="K359"/>
-      <c r="L359"/>
-    </row>
-    <row r="360" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="360" spans="1:11" s="9" customFormat="1">
       <c r="A360" s="9">
         <v>24050081</v>
       </c>
@@ -19957,11 +19521,8 @@
       <c r="J360" s="9">
         <v>3</v>
       </c>
-      <c r="L360" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="361" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="361" spans="1:11" s="9" customFormat="1">
       <c r="A361" s="9">
         <v>24050082</v>
       </c>
@@ -19983,11 +19544,8 @@
       <c r="J361" s="9">
         <v>3</v>
       </c>
-      <c r="L361" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="362" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="362" spans="1:11" s="9" customFormat="1">
       <c r="A362" s="9">
         <v>24050084</v>
       </c>
@@ -20013,9 +19571,8 @@
         <v>3</v>
       </c>
       <c r="K362"/>
-      <c r="L362"/>
-    </row>
-    <row r="363" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="363" spans="1:11" s="9" customFormat="1">
       <c r="A363" s="9">
         <v>24050085</v>
       </c>
@@ -20050,7 +19607,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="364" spans="1:12" s="9" customFormat="1">
+    <row r="364" spans="1:11" s="9" customFormat="1">
       <c r="A364" s="9">
         <v>24050086</v>
       </c>
@@ -20072,11 +19629,8 @@
       <c r="J364" s="9">
         <v>3</v>
       </c>
-      <c r="L364" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="365" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="365" spans="1:11" s="9" customFormat="1">
       <c r="A365" s="9">
         <v>24050088</v>
       </c>
@@ -20099,7 +19653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:12" s="9" customFormat="1">
+    <row r="366" spans="1:11" s="9" customFormat="1">
       <c r="A366" s="9">
         <v>24050090</v>
       </c>
@@ -20125,9 +19679,8 @@
         <v>3</v>
       </c>
       <c r="K366"/>
-      <c r="L366"/>
-    </row>
-    <row r="367" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="367" spans="1:11" s="9" customFormat="1">
       <c r="A367" s="9">
         <v>24050091</v>
       </c>
@@ -20158,11 +19711,8 @@
       <c r="K367" s="9" t="s">
         <v>1911</v>
       </c>
-      <c r="L367" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="368" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="368" spans="1:11" s="9" customFormat="1">
       <c r="A368" s="9">
         <v>24050093</v>
       </c>
@@ -20196,9 +19746,8 @@
       <c r="K368" t="s">
         <v>735</v>
       </c>
-      <c r="L368"/>
-    </row>
-    <row r="369" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="369" spans="1:11" s="9" customFormat="1">
       <c r="A369" s="9">
         <v>24050094</v>
       </c>
@@ -20224,9 +19773,8 @@
         <v>3</v>
       </c>
       <c r="K369"/>
-      <c r="L369"/>
-    </row>
-    <row r="370" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="370" spans="1:11" s="9" customFormat="1">
       <c r="A370" s="9">
         <v>24050095</v>
       </c>
@@ -20248,11 +19796,8 @@
       <c r="J370" s="9">
         <v>3</v>
       </c>
-      <c r="L370" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="371" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="371" spans="1:11" s="9" customFormat="1">
       <c r="A371" s="9">
         <v>24050096</v>
       </c>
@@ -20278,9 +19823,8 @@
         <v>3</v>
       </c>
       <c r="K371"/>
-      <c r="L371"/>
-    </row>
-    <row r="372" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="372" spans="1:11" s="9" customFormat="1">
       <c r="A372" s="9">
         <v>24050097</v>
       </c>
@@ -20308,9 +19852,8 @@
         <v>2</v>
       </c>
       <c r="K372"/>
-      <c r="L372"/>
-    </row>
-    <row r="373" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="373" spans="1:11" s="9" customFormat="1">
       <c r="A373" s="9">
         <v>24050098</v>
       </c>
@@ -20332,11 +19875,8 @@
       <c r="J373" s="9">
         <v>3</v>
       </c>
-      <c r="L373" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="374" spans="1:11" s="9" customFormat="1">
       <c r="A374" s="9">
         <v>24050100</v>
       </c>
@@ -20368,9 +19908,8 @@
       <c r="K374" t="s">
         <v>1019</v>
       </c>
-      <c r="L374"/>
-    </row>
-    <row r="375" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="375" spans="1:11" s="9" customFormat="1">
       <c r="A375" s="9">
         <v>24050101</v>
       </c>
@@ -20396,9 +19935,8 @@
         <v>3</v>
       </c>
       <c r="K375"/>
-      <c r="L375"/>
-    </row>
-    <row r="376" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="376" spans="1:11" s="9" customFormat="1">
       <c r="A376" s="9">
         <v>24050103</v>
       </c>
@@ -20429,11 +19967,8 @@
       <c r="K376" s="9" t="s">
         <v>2147</v>
       </c>
-      <c r="L376" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="377" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="377" spans="1:11" s="9" customFormat="1">
       <c r="A377" s="9">
         <v>24050106</v>
       </c>
@@ -20455,11 +19990,8 @@
       <c r="J377" s="9">
         <v>3</v>
       </c>
-      <c r="L377" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="378" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="378" spans="1:11" s="9" customFormat="1">
       <c r="A378" s="9">
         <v>24050107</v>
       </c>
@@ -20491,9 +20023,8 @@
       <c r="K378" t="s">
         <v>1020</v>
       </c>
-      <c r="L378"/>
-    </row>
-    <row r="379" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="379" spans="1:11" s="9" customFormat="1">
       <c r="A379" s="9">
         <v>24050108</v>
       </c>
@@ -20519,9 +20050,8 @@
         <v>3</v>
       </c>
       <c r="K379"/>
-      <c r="L379"/>
-    </row>
-    <row r="380" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="380" spans="1:11" s="9" customFormat="1">
       <c r="A380" s="9">
         <v>24050109</v>
       </c>
@@ -20543,11 +20073,8 @@
       <c r="J380" s="9">
         <v>3</v>
       </c>
-      <c r="L380" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="381" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="381" spans="1:11" s="9" customFormat="1">
       <c r="A381" s="9">
         <v>24050110</v>
       </c>
@@ -20577,9 +20104,8 @@
         <v>3</v>
       </c>
       <c r="K381"/>
-      <c r="L381"/>
-    </row>
-    <row r="382" spans="1:12" s="9" customFormat="1" ht="141">
+    </row>
+    <row r="382" spans="1:11" s="9" customFormat="1" ht="141">
       <c r="A382" s="9">
         <v>24050111</v>
       </c>
@@ -20609,9 +20135,8 @@
         <v>2</v>
       </c>
       <c r="K382"/>
-      <c r="L382"/>
-    </row>
-    <row r="383" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="383" spans="1:11" s="9" customFormat="1">
       <c r="A383" s="9">
         <v>24050112</v>
       </c>
@@ -20642,11 +20167,8 @@
       <c r="K383" s="9" t="s">
         <v>1847</v>
       </c>
-      <c r="L383" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="384" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="384" spans="1:11" s="9" customFormat="1">
       <c r="A384" s="9">
         <v>24050113</v>
       </c>
@@ -20676,9 +20198,8 @@
       <c r="K384" s="6" t="s">
         <v>1033</v>
       </c>
-      <c r="L384"/>
-    </row>
-    <row r="385" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="385" spans="1:11" s="9" customFormat="1">
       <c r="A385" s="9">
         <v>24050114</v>
       </c>
@@ -20712,9 +20233,8 @@
       <c r="K385" t="s">
         <v>1022</v>
       </c>
-      <c r="L385"/>
-    </row>
-    <row r="386" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="386" spans="1:11" s="9" customFormat="1">
       <c r="A386" s="9">
         <v>24050116</v>
       </c>
@@ -20748,9 +20268,8 @@
       <c r="K386" t="s">
         <v>1023</v>
       </c>
-      <c r="L386"/>
-    </row>
-    <row r="387" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="387" spans="1:11" s="9" customFormat="1">
       <c r="A387" s="9">
         <v>24050117</v>
       </c>
@@ -20772,11 +20291,8 @@
       <c r="J387" s="9">
         <v>3</v>
       </c>
-      <c r="L387" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="388" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="388" spans="1:11" s="9" customFormat="1">
       <c r="A388" s="9">
         <v>24050118</v>
       </c>
@@ -20810,9 +20326,8 @@
       <c r="K388" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="L388"/>
-    </row>
-    <row r="389" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="389" spans="1:11" s="9" customFormat="1">
       <c r="A389" s="9">
         <v>24050119</v>
       </c>
@@ -20842,9 +20357,8 @@
       <c r="K389" s="6" t="s">
         <v>1034</v>
       </c>
-      <c r="L389"/>
-    </row>
-    <row r="390" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="390" spans="1:11" s="9" customFormat="1">
       <c r="A390" s="9">
         <v>24050120</v>
       </c>
@@ -20873,7 +20387,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="391" spans="1:12" s="9" customFormat="1">
+    <row r="391" spans="1:11" s="9" customFormat="1">
       <c r="A391" s="9">
         <v>24050122</v>
       </c>
@@ -20896,7 +20410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="392" spans="1:12" s="9" customFormat="1">
+    <row r="392" spans="1:11" s="9" customFormat="1">
       <c r="A392" s="9">
         <v>24050123</v>
       </c>
@@ -20926,9 +20440,8 @@
       <c r="K392" s="6" t="s">
         <v>1035</v>
       </c>
-      <c r="L392"/>
-    </row>
-    <row r="393" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="393" spans="1:11" s="9" customFormat="1">
       <c r="A393" s="9">
         <v>24050124</v>
       </c>
@@ -20957,7 +20470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="1:12" s="9" customFormat="1">
+    <row r="394" spans="1:11" s="9" customFormat="1">
       <c r="A394" s="9">
         <v>24050125</v>
       </c>
@@ -20982,11 +20495,8 @@
       <c r="J394" s="9">
         <v>3</v>
       </c>
-      <c r="L394" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="395" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="395" spans="1:11" s="9" customFormat="1">
       <c r="A395" s="9">
         <v>24050126</v>
       </c>
@@ -21020,9 +20530,8 @@
       <c r="K395" t="s">
         <v>1025</v>
       </c>
-      <c r="L395"/>
-    </row>
-    <row r="396" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="396" spans="1:11" s="9" customFormat="1">
       <c r="A396" s="9">
         <v>24050127</v>
       </c>
@@ -21051,7 +20560,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="397" spans="1:12" s="9" customFormat="1">
+    <row r="397" spans="1:11" s="9" customFormat="1">
       <c r="A397" s="9">
         <v>24050129</v>
       </c>
@@ -21073,11 +20582,8 @@
       <c r="J397" s="9">
         <v>3</v>
       </c>
-      <c r="L397" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="398" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="398" spans="1:11" s="9" customFormat="1">
       <c r="A398" s="9">
         <v>24050131</v>
       </c>
@@ -21108,11 +20614,8 @@
       <c r="K398" s="9" t="s">
         <v>1859</v>
       </c>
-      <c r="L398" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="399" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="399" spans="1:11" s="9" customFormat="1">
       <c r="A399" s="9">
         <v>24050132</v>
       </c>
@@ -21146,9 +20649,8 @@
       <c r="K399" t="s">
         <v>737</v>
       </c>
-      <c r="L399"/>
-    </row>
-    <row r="400" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="400" spans="1:11" s="9" customFormat="1">
       <c r="A400" s="9">
         <v>24050133</v>
       </c>
@@ -21170,11 +20672,8 @@
       <c r="J400" s="9">
         <v>3</v>
       </c>
-      <c r="L400" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="401" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="401" spans="1:11" s="9" customFormat="1">
       <c r="A401" s="9">
         <v>24050134</v>
       </c>
@@ -21205,11 +20704,8 @@
       <c r="K401" s="9" t="s">
         <v>1850</v>
       </c>
-      <c r="L401" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="402" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="402" spans="1:11" s="9" customFormat="1">
       <c r="A402" s="9">
         <v>24050135</v>
       </c>
@@ -21244,7 +20740,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="403" spans="1:12" s="9" customFormat="1">
+    <row r="403" spans="1:11" s="9" customFormat="1">
       <c r="A403" s="9">
         <v>24050136</v>
       </c>
@@ -21270,9 +20766,8 @@
         <v>3</v>
       </c>
       <c r="K403"/>
-      <c r="L403"/>
-    </row>
-    <row r="404" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="404" spans="1:11" s="9" customFormat="1">
       <c r="A404" s="9">
         <v>24050137</v>
       </c>
@@ -21298,9 +20793,8 @@
         <v>3</v>
       </c>
       <c r="K404"/>
-      <c r="L404"/>
-    </row>
-    <row r="405" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="405" spans="1:11" s="33" customFormat="1">
       <c r="A405" s="9">
         <v>24050138</v>
       </c>
@@ -21330,9 +20824,8 @@
         <v>3</v>
       </c>
       <c r="K405"/>
-      <c r="L405"/>
-    </row>
-    <row r="406" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="406" spans="1:11" s="9" customFormat="1">
       <c r="A406" s="9">
         <v>24050139</v>
       </c>
@@ -21366,9 +20859,8 @@
       <c r="K406" t="s">
         <v>982</v>
       </c>
-      <c r="L406"/>
-    </row>
-    <row r="407" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="407" spans="1:11" s="9" customFormat="1">
       <c r="A407" s="9">
         <v>24050140</v>
       </c>
@@ -21403,7 +20895,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="408" spans="1:12" s="33" customFormat="1">
+    <row r="408" spans="1:11" s="33" customFormat="1">
       <c r="A408" s="9">
         <v>24050141</v>
       </c>
@@ -21437,9 +20929,8 @@
       <c r="K408" t="s">
         <v>985</v>
       </c>
-      <c r="L408"/>
-    </row>
-    <row r="409" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="409" spans="1:11" s="9" customFormat="1">
       <c r="A409" s="9">
         <v>24050142</v>
       </c>
@@ -21473,9 +20964,8 @@
       <c r="K409" t="s">
         <v>739</v>
       </c>
-      <c r="L409"/>
-    </row>
-    <row r="410" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="410" spans="1:11" s="9" customFormat="1">
       <c r="A410" s="9">
         <v>24050143</v>
       </c>
@@ -21510,7 +21000,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="411" spans="1:12" s="9" customFormat="1">
+    <row r="411" spans="1:11" s="9" customFormat="1">
       <c r="A411" s="9">
         <v>24050145</v>
       </c>
@@ -21544,9 +21034,8 @@
       <c r="K411" t="s">
         <v>988</v>
       </c>
-      <c r="L411"/>
-    </row>
-    <row r="412" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="412" spans="1:11" s="9" customFormat="1">
       <c r="A412" s="9">
         <v>24050146</v>
       </c>
@@ -21581,7 +21070,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="413" spans="1:12" s="9" customFormat="1" ht="14.7" customHeight="1">
+    <row r="413" spans="1:11" s="9" customFormat="1" ht="14.7" customHeight="1">
       <c r="A413" s="9">
         <v>24050147</v>
       </c>
@@ -21612,11 +21101,8 @@
       <c r="K413" s="9" t="s">
         <v>2084</v>
       </c>
-      <c r="L413" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="414" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="414" spans="1:11" s="9" customFormat="1">
       <c r="A414" s="9">
         <v>24050149</v>
       </c>
@@ -21650,11 +21136,8 @@
       <c r="K414" s="9" t="s">
         <v>1929</v>
       </c>
-      <c r="L414" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="415" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="415" spans="1:11" s="9" customFormat="1">
       <c r="A415" s="9">
         <v>24050150</v>
       </c>
@@ -21686,9 +21169,8 @@
       <c r="K415" t="s">
         <v>737</v>
       </c>
-      <c r="L415"/>
-    </row>
-    <row r="416" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="416" spans="1:11" s="9" customFormat="1">
       <c r="A416" s="9">
         <v>24050151</v>
       </c>
@@ -21722,9 +21204,8 @@
       <c r="K416" t="s">
         <v>990</v>
       </c>
-      <c r="L416"/>
-    </row>
-    <row r="417" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="417" spans="1:11" s="9" customFormat="1">
       <c r="A417" s="9">
         <v>24050152</v>
       </c>
@@ -21758,9 +21239,8 @@
       <c r="K417" t="s">
         <v>992</v>
       </c>
-      <c r="L417"/>
-    </row>
-    <row r="418" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="418" spans="1:11" s="9" customFormat="1">
       <c r="A418" s="9">
         <v>24050153</v>
       </c>
@@ -21788,9 +21268,8 @@
         <v>3</v>
       </c>
       <c r="K418"/>
-      <c r="L418"/>
-    </row>
-    <row r="419" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="419" spans="1:11" s="9" customFormat="1">
       <c r="A419" s="9">
         <v>24050155</v>
       </c>
@@ -21821,11 +21300,8 @@
       <c r="K419" s="9" t="s">
         <v>2123</v>
       </c>
-      <c r="L419" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="420" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="420" spans="1:11" s="9" customFormat="1">
       <c r="A420" s="9">
         <v>24050156</v>
       </c>
@@ -21853,9 +21329,8 @@
         <v>3</v>
       </c>
       <c r="K420"/>
-      <c r="L420"/>
-    </row>
-    <row r="421" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="421" spans="1:11" s="9" customFormat="1">
       <c r="A421" s="9">
         <v>24050157</v>
       </c>
@@ -21889,9 +21364,8 @@
       <c r="K421" t="s">
         <v>737</v>
       </c>
-      <c r="L421"/>
-    </row>
-    <row r="422" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="422" spans="1:11" s="9" customFormat="1">
       <c r="A422" s="9">
         <v>24050158</v>
       </c>
@@ -21923,7 +21397,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="423" spans="1:12" s="9" customFormat="1">
+    <row r="423" spans="1:11" s="9" customFormat="1">
       <c r="A423" s="9">
         <v>24050159</v>
       </c>
@@ -21954,11 +21428,8 @@
       <c r="K423" s="9" t="s">
         <v>1024</v>
       </c>
-      <c r="L423" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="424" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="424" spans="1:11" s="9" customFormat="1">
       <c r="A424" s="9">
         <v>24050161</v>
       </c>
@@ -21992,9 +21463,8 @@
       <c r="K424" t="s">
         <v>994</v>
       </c>
-      <c r="L424"/>
-    </row>
-    <row r="425" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="425" spans="1:11" s="9" customFormat="1">
       <c r="A425" s="9">
         <v>24050163</v>
       </c>
@@ -22020,9 +21490,8 @@
         <v>3</v>
       </c>
       <c r="K425"/>
-      <c r="L425"/>
-    </row>
-    <row r="426" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="426" spans="1:11" s="9" customFormat="1">
       <c r="A426" s="9">
         <v>24050165</v>
       </c>
@@ -22044,11 +21513,8 @@
       <c r="J426" s="9">
         <v>3</v>
       </c>
-      <c r="L426" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="427" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="427" spans="1:11" s="9" customFormat="1">
       <c r="A427" s="9">
         <v>24060002</v>
       </c>
@@ -22082,9 +21548,8 @@
       <c r="K427" s="14" t="s">
         <v>1039</v>
       </c>
-      <c r="L427" s="14"/>
-    </row>
-    <row r="428" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="428" spans="1:11" s="9" customFormat="1">
       <c r="A428" s="9">
         <v>24060003</v>
       </c>
@@ -22118,9 +21583,8 @@
       <c r="K428" s="5" t="s">
         <v>1042</v>
       </c>
-      <c r="L428" s="4"/>
-    </row>
-    <row r="429" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="429" spans="1:11" s="9" customFormat="1">
       <c r="A429" s="9">
         <v>24060004</v>
       </c>
@@ -22155,7 +21619,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="430" spans="1:12" s="9" customFormat="1">
+    <row r="430" spans="1:11" s="9" customFormat="1">
       <c r="A430" s="9">
         <v>24060006</v>
       </c>
@@ -22189,9 +21653,8 @@
       <c r="K430" t="s">
         <v>1043</v>
       </c>
-      <c r="L430"/>
-    </row>
-    <row r="431" spans="1:12" s="9" customFormat="1" ht="15">
+    </row>
+    <row r="431" spans="1:11" s="9" customFormat="1" ht="15">
       <c r="A431" s="9">
         <v>24060007</v>
       </c>
@@ -22226,7 +21689,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="432" spans="1:12" s="9" customFormat="1">
+    <row r="432" spans="1:11" s="9" customFormat="1">
       <c r="A432" s="9">
         <v>24060008</v>
       </c>
@@ -22260,9 +21723,8 @@
       <c r="K432" t="s">
         <v>1045</v>
       </c>
-      <c r="L432"/>
-    </row>
-    <row r="433" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="433" spans="1:11" s="9" customFormat="1">
       <c r="A433" s="9">
         <v>24060009</v>
       </c>
@@ -22288,9 +21750,8 @@
         <v>3</v>
       </c>
       <c r="K433"/>
-      <c r="L433"/>
-    </row>
-    <row r="434" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="434" spans="1:11" s="9" customFormat="1">
       <c r="A434" s="9">
         <v>24060011</v>
       </c>
@@ -22312,11 +21773,8 @@
       <c r="J434" s="9">
         <v>3</v>
       </c>
-      <c r="L434" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="435" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="435" spans="1:11" s="9" customFormat="1">
       <c r="A435" s="9">
         <v>24060012</v>
       </c>
@@ -22350,9 +21808,8 @@
       <c r="K435" t="s">
         <v>1048</v>
       </c>
-      <c r="L435"/>
-    </row>
-    <row r="436" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="436" spans="1:11" s="9" customFormat="1">
       <c r="A436" s="9">
         <v>24060013</v>
       </c>
@@ -22381,7 +21838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:12" s="9" customFormat="1">
+    <row r="437" spans="1:11" s="9" customFormat="1">
       <c r="A437" s="9">
         <v>24060014</v>
       </c>
@@ -22415,11 +21872,8 @@
       <c r="K437" s="9" t="s">
         <v>1313</v>
       </c>
-      <c r="L437" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="438" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="438" spans="1:11" s="9" customFormat="1">
       <c r="A438" s="9">
         <v>24060016</v>
       </c>
@@ -22453,11 +21907,8 @@
       <c r="K438" s="9" t="s">
         <v>1957</v>
       </c>
-      <c r="L438" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="439" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="439" spans="1:11" s="9" customFormat="1">
       <c r="A439" s="9">
         <v>24060017</v>
       </c>
@@ -22492,7 +21943,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="440" spans="1:12" s="9" customFormat="1">
+    <row r="440" spans="1:11" s="9" customFormat="1">
       <c r="A440" s="9">
         <v>24060018</v>
       </c>
@@ -22526,9 +21977,8 @@
       <c r="K440" s="6" t="s">
         <v>1097</v>
       </c>
-      <c r="L440"/>
-    </row>
-    <row r="441" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="441" spans="1:11" s="9" customFormat="1">
       <c r="A441" s="9">
         <v>24060019</v>
       </c>
@@ -22563,7 +22013,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="442" spans="1:12" s="9" customFormat="1">
+    <row r="442" spans="1:11" s="9" customFormat="1">
       <c r="A442" s="9">
         <v>24060022</v>
       </c>
@@ -22589,9 +22039,8 @@
         <v>3</v>
       </c>
       <c r="K442"/>
-      <c r="L442"/>
-    </row>
-    <row r="443" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="443" spans="1:11" s="9" customFormat="1">
       <c r="A443" s="9">
         <v>24060023</v>
       </c>
@@ -22625,11 +22074,8 @@
       <c r="K443" s="9" t="s">
         <v>2001</v>
       </c>
-      <c r="L443" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="444" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="444" spans="1:11" s="9" customFormat="1">
       <c r="A444" s="9">
         <v>24060024</v>
       </c>
@@ -22663,9 +22109,8 @@
       <c r="K444" t="s">
         <v>1067</v>
       </c>
-      <c r="L444"/>
-    </row>
-    <row r="445" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="445" spans="1:11" s="9" customFormat="1">
       <c r="A445" s="9">
         <v>24060025</v>
       </c>
@@ -22699,9 +22144,8 @@
       <c r="K445" s="4" t="s">
         <v>1041</v>
       </c>
-      <c r="L445" s="4"/>
-    </row>
-    <row r="446" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="446" spans="1:11" s="9" customFormat="1">
       <c r="A446" s="9">
         <v>24060026</v>
       </c>
@@ -22723,11 +22167,8 @@
       <c r="J446" s="9">
         <v>3</v>
       </c>
-      <c r="L446" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="447" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="447" spans="1:11" s="9" customFormat="1">
       <c r="A447" s="9">
         <v>24060027</v>
       </c>
@@ -22749,11 +22190,8 @@
       <c r="J447" s="9">
         <v>3</v>
       </c>
-      <c r="L447" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="448" spans="1:12" s="9" customFormat="1" ht="37.200000000000003" customHeight="1">
+    </row>
+    <row r="448" spans="1:11" s="9" customFormat="1" ht="37.200000000000003" customHeight="1">
       <c r="A448" s="9">
         <v>24070001</v>
       </c>
@@ -22781,9 +22219,8 @@
         <v>3</v>
       </c>
       <c r="K448" s="14"/>
-      <c r="L448" s="14"/>
-    </row>
-    <row r="449" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="449" spans="1:11" s="9" customFormat="1">
       <c r="A449" s="9">
         <v>24070002</v>
       </c>
@@ -22805,11 +22242,8 @@
       <c r="J449" s="9">
         <v>3</v>
       </c>
-      <c r="L449" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="450" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="450" spans="1:11" s="9" customFormat="1">
       <c r="A450" s="9">
         <v>24070003</v>
       </c>
@@ -22843,9 +22277,8 @@
       <c r="K450" t="s">
         <v>1053</v>
       </c>
-      <c r="L450"/>
-    </row>
-    <row r="451" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="451" spans="1:11" s="9" customFormat="1">
       <c r="A451" s="9">
         <v>24070004</v>
       </c>
@@ -22871,9 +22304,8 @@
         <v>3</v>
       </c>
       <c r="K451"/>
-      <c r="L451"/>
-    </row>
-    <row r="452" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="452" spans="1:11" s="9" customFormat="1">
       <c r="A452" s="9">
         <v>24070007</v>
       </c>
@@ -22905,9 +22337,8 @@
       <c r="K452" t="s">
         <v>1055</v>
       </c>
-      <c r="L452"/>
-    </row>
-    <row r="453" spans="1:12" s="34" customFormat="1">
+    </row>
+    <row r="453" spans="1:11" s="34" customFormat="1">
       <c r="A453" s="9">
         <v>24070008</v>
       </c>
@@ -22933,11 +22364,8 @@
         <v>3</v>
       </c>
       <c r="K453" s="9"/>
-      <c r="L453" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="454" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="454" spans="1:11" s="9" customFormat="1">
       <c r="A454" s="9">
         <v>24070009</v>
       </c>
@@ -22965,9 +22393,8 @@
         <v>3</v>
       </c>
       <c r="K454" s="4"/>
-      <c r="L454" s="4"/>
-    </row>
-    <row r="455" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="455" spans="1:11" s="9" customFormat="1">
       <c r="A455" s="9">
         <v>24070010</v>
       </c>
@@ -22995,9 +22422,8 @@
         <v>3</v>
       </c>
       <c r="K455"/>
-      <c r="L455"/>
-    </row>
-    <row r="456" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="456" spans="1:11" s="9" customFormat="1">
       <c r="A456" s="9">
         <v>24070011</v>
       </c>
@@ -23019,11 +22445,8 @@
       <c r="J456" s="9">
         <v>3</v>
       </c>
-      <c r="L456" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="457" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="457" spans="1:11" s="9" customFormat="1">
       <c r="A457" s="9">
         <v>24070012</v>
       </c>
@@ -23045,11 +22468,8 @@
       <c r="J457" s="9">
         <v>3</v>
       </c>
-      <c r="L457" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="458" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="458" spans="1:11" s="9" customFormat="1">
       <c r="A458" s="9">
         <v>24070013</v>
       </c>
@@ -23071,11 +22491,8 @@
       <c r="J458" s="9">
         <v>3</v>
       </c>
-      <c r="L458" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="459" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="459" spans="1:11" s="9" customFormat="1">
       <c r="A459" s="9">
         <v>24070015</v>
       </c>
@@ -23103,9 +22520,8 @@
         <v>3</v>
       </c>
       <c r="K459"/>
-      <c r="L459"/>
-    </row>
-    <row r="460" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="460" spans="1:11" s="9" customFormat="1">
       <c r="A460" s="9">
         <v>24070016</v>
       </c>
@@ -23140,7 +22556,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="461" spans="1:12" s="9" customFormat="1">
+    <row r="461" spans="1:11" s="9" customFormat="1">
       <c r="A461" s="9">
         <v>24070017</v>
       </c>
@@ -23168,9 +22584,8 @@
         <v>3</v>
       </c>
       <c r="K461"/>
-      <c r="L461"/>
-    </row>
-    <row r="462" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="462" spans="1:11" s="9" customFormat="1">
       <c r="A462" s="9">
         <v>24070018</v>
       </c>
@@ -23198,9 +22613,8 @@
         <v>3</v>
       </c>
       <c r="K462"/>
-      <c r="L462"/>
-    </row>
-    <row r="463" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="463" spans="1:11" s="9" customFormat="1">
       <c r="A463" s="9">
         <v>24070019</v>
       </c>
@@ -23234,9 +22648,8 @@
       <c r="K463" t="s">
         <v>1068</v>
       </c>
-      <c r="L463"/>
-    </row>
-    <row r="464" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="464" spans="1:11" s="9" customFormat="1">
       <c r="A464" s="9">
         <v>24070020</v>
       </c>
@@ -23266,9 +22679,8 @@
       <c r="K464" s="6" t="s">
         <v>1099</v>
       </c>
-      <c r="L464"/>
-    </row>
-    <row r="465" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="465" spans="1:11" s="9" customFormat="1">
       <c r="A465" s="9">
         <v>24070022</v>
       </c>
@@ -23294,7 +22706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="466" spans="1:12" s="9" customFormat="1">
+    <row r="466" spans="1:11" s="9" customFormat="1">
       <c r="A466" s="9">
         <v>24070023</v>
       </c>
@@ -23322,9 +22734,8 @@
         <v>3</v>
       </c>
       <c r="K466"/>
-      <c r="L466"/>
-    </row>
-    <row r="467" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="467" spans="1:11" s="9" customFormat="1">
       <c r="A467" s="9">
         <v>24070024</v>
       </c>
@@ -23356,9 +22767,8 @@
       <c r="K467" s="6" t="s">
         <v>1099</v>
       </c>
-      <c r="L467"/>
-    </row>
-    <row r="468" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="468" spans="1:11" s="9" customFormat="1">
       <c r="A468" s="9">
         <v>24070025</v>
       </c>
@@ -23384,9 +22794,8 @@
         <v>3</v>
       </c>
       <c r="K468"/>
-      <c r="L468"/>
-    </row>
-    <row r="469" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="469" spans="1:11" s="9" customFormat="1">
       <c r="A469" s="9">
         <v>24070028</v>
       </c>
@@ -23412,7 +22821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="470" spans="1:12" s="9" customFormat="1">
+    <row r="470" spans="1:11" s="9" customFormat="1">
       <c r="A470" s="9">
         <v>24070029</v>
       </c>
@@ -23446,9 +22855,8 @@
       <c r="K470" t="s">
         <v>1069</v>
       </c>
-      <c r="L470"/>
-    </row>
-    <row r="471" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="471" spans="1:11" s="9" customFormat="1">
       <c r="A471" s="9">
         <v>24070031</v>
       </c>
@@ -23471,7 +22879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="1:12" s="9" customFormat="1">
+    <row r="472" spans="1:11" s="9" customFormat="1">
       <c r="A472" s="9">
         <v>24070033</v>
       </c>
@@ -23494,7 +22902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="473" spans="1:12" s="9" customFormat="1">
+    <row r="473" spans="1:11" s="9" customFormat="1">
       <c r="A473" s="9">
         <v>24070034</v>
       </c>
@@ -23528,9 +22936,8 @@
       <c r="K473" t="s">
         <v>1070</v>
       </c>
-      <c r="L473"/>
-    </row>
-    <row r="474" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="474" spans="1:11" s="9" customFormat="1">
       <c r="A474" s="9">
         <v>24070035</v>
       </c>
@@ -23564,11 +22971,8 @@
       <c r="K474" s="9" t="s">
         <v>1023</v>
       </c>
-      <c r="L474" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="475" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="475" spans="1:11" s="9" customFormat="1">
       <c r="A475" s="9">
         <v>24070036</v>
       </c>
@@ -23596,9 +23000,8 @@
         <v>3</v>
       </c>
       <c r="K475"/>
-      <c r="L475"/>
-    </row>
-    <row r="476" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="476" spans="1:11" s="9" customFormat="1">
       <c r="A476" s="9">
         <v>24070037</v>
       </c>
@@ -23620,11 +23023,8 @@
       <c r="J476" s="9">
         <v>3</v>
       </c>
-      <c r="L476" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="477" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="477" spans="1:11" s="9" customFormat="1">
       <c r="A477" s="9">
         <v>24070038</v>
       </c>
@@ -23650,9 +23050,8 @@
         <v>3</v>
       </c>
       <c r="K477"/>
-      <c r="L477"/>
-    </row>
-    <row r="478" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="478" spans="1:11" s="9" customFormat="1">
       <c r="A478" s="9">
         <v>24070039</v>
       </c>
@@ -23678,9 +23077,8 @@
         <v>3</v>
       </c>
       <c r="K478"/>
-      <c r="L478"/>
-    </row>
-    <row r="479" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="479" spans="1:11" s="9" customFormat="1">
       <c r="A479" s="9">
         <v>24070040</v>
       </c>
@@ -23708,9 +23106,8 @@
         <v>3</v>
       </c>
       <c r="K479"/>
-      <c r="L479"/>
-    </row>
-    <row r="480" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="480" spans="1:11" s="9" customFormat="1">
       <c r="A480" s="9">
         <v>24070041</v>
       </c>
@@ -23732,11 +23129,8 @@
       <c r="J480" s="9">
         <v>3</v>
       </c>
-      <c r="L480" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="481" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="481" spans="1:11" s="9" customFormat="1">
       <c r="A481" s="9">
         <v>24070042</v>
       </c>
@@ -23762,9 +23156,8 @@
         <v>3</v>
       </c>
       <c r="K481"/>
-      <c r="L481"/>
-    </row>
-    <row r="482" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="482" spans="1:11" s="9" customFormat="1">
       <c r="A482" s="9">
         <v>24070043</v>
       </c>
@@ -23790,9 +23183,8 @@
         <v>3</v>
       </c>
       <c r="K482"/>
-      <c r="L482"/>
-    </row>
-    <row r="483" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="483" spans="1:11" s="9" customFormat="1">
       <c r="A483" s="9">
         <v>24070046</v>
       </c>
@@ -23820,9 +23212,8 @@
         <v>3</v>
       </c>
       <c r="K483"/>
-      <c r="L483"/>
-    </row>
-    <row r="484" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="484" spans="1:11" s="9" customFormat="1">
       <c r="A484" s="9">
         <v>24070048</v>
       </c>
@@ -23848,9 +23239,8 @@
         <v>3</v>
       </c>
       <c r="K484"/>
-      <c r="L484"/>
-    </row>
-    <row r="485" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="485" spans="1:11" s="9" customFormat="1">
       <c r="A485" s="9">
         <v>24070049</v>
       </c>
@@ -23884,9 +23274,8 @@
       <c r="K485" t="s">
         <v>1059</v>
       </c>
-      <c r="L485"/>
-    </row>
-    <row r="486" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="486" spans="1:11" s="9" customFormat="1">
       <c r="A486" s="9">
         <v>24070050</v>
       </c>
@@ -23912,9 +23301,8 @@
         <v>3</v>
       </c>
       <c r="K486"/>
-      <c r="L486"/>
-    </row>
-    <row r="487" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="487" spans="1:11" s="9" customFormat="1">
       <c r="A487" s="9">
         <v>24070051</v>
       </c>
@@ -23942,9 +23330,8 @@
         <v>3</v>
       </c>
       <c r="K487"/>
-      <c r="L487"/>
-    </row>
-    <row r="488" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="488" spans="1:11" s="9" customFormat="1">
       <c r="A488" s="9">
         <v>24070052</v>
       </c>
@@ -23970,9 +23357,8 @@
         <v>3</v>
       </c>
       <c r="K488"/>
-      <c r="L488"/>
-    </row>
-    <row r="489" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="489" spans="1:11" s="9" customFormat="1">
       <c r="A489" s="9">
         <v>24070053</v>
       </c>
@@ -23998,9 +23384,8 @@
         <v>3</v>
       </c>
       <c r="K489"/>
-      <c r="L489"/>
-    </row>
-    <row r="490" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="490" spans="1:11" s="9" customFormat="1">
       <c r="A490" s="9">
         <v>24070054</v>
       </c>
@@ -24023,7 +23408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="491" spans="1:12" s="9" customFormat="1">
+    <row r="491" spans="1:11" s="9" customFormat="1">
       <c r="A491" s="9">
         <v>24070055</v>
       </c>
@@ -24049,9 +23434,8 @@
         <v>3</v>
       </c>
       <c r="K491"/>
-      <c r="L491"/>
-    </row>
-    <row r="492" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="492" spans="1:11" s="9" customFormat="1">
       <c r="A492" s="9">
         <v>24070057</v>
       </c>
@@ -24077,9 +23461,8 @@
         <v>3</v>
       </c>
       <c r="K492"/>
-      <c r="L492"/>
-    </row>
-    <row r="493" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="493" spans="1:11" s="9" customFormat="1">
       <c r="A493" s="9">
         <v>24070059</v>
       </c>
@@ -24113,9 +23496,8 @@
       <c r="K493" s="4" t="s">
         <v>1071</v>
       </c>
-      <c r="L493" s="4"/>
-    </row>
-    <row r="494" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="494" spans="1:11" s="9" customFormat="1">
       <c r="A494" s="9">
         <v>24070060</v>
       </c>
@@ -24137,11 +23519,8 @@
       <c r="J494" s="9">
         <v>3</v>
       </c>
-      <c r="L494" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="495" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="495" spans="1:11" s="9" customFormat="1">
       <c r="A495" s="9">
         <v>24070061</v>
       </c>
@@ -24175,9 +23554,8 @@
       <c r="K495" t="s">
         <v>1102</v>
       </c>
-      <c r="L495"/>
-    </row>
-    <row r="496" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="496" spans="1:11" s="9" customFormat="1">
       <c r="A496" s="9">
         <v>24070062</v>
       </c>
@@ -24211,9 +23589,8 @@
       <c r="K496" t="s">
         <v>1103</v>
       </c>
-      <c r="L496"/>
-    </row>
-    <row r="497" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="497" spans="1:11" s="9" customFormat="1">
       <c r="A497" s="9">
         <v>24070066</v>
       </c>
@@ -24235,11 +23612,8 @@
       <c r="J497" s="9">
         <v>3</v>
       </c>
-      <c r="L497" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="498" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="498" spans="1:11" s="9" customFormat="1">
       <c r="A498" s="9">
         <v>24070067</v>
       </c>
@@ -24265,7 +23639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="499" spans="1:12" s="9" customFormat="1">
+    <row r="499" spans="1:11" s="9" customFormat="1">
       <c r="A499" s="9">
         <v>24070068</v>
       </c>
@@ -24299,9 +23673,8 @@
       <c r="K499" t="s">
         <v>1104</v>
       </c>
-      <c r="L499"/>
-    </row>
-    <row r="500" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="500" spans="1:11" s="9" customFormat="1">
       <c r="A500" s="9">
         <v>24070069</v>
       </c>
@@ -24327,7 +23700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="501" spans="1:12" s="9" customFormat="1">
+    <row r="501" spans="1:11" s="9" customFormat="1">
       <c r="A501" s="9">
         <v>24070071</v>
       </c>
@@ -24353,9 +23726,8 @@
         <v>3</v>
       </c>
       <c r="K501"/>
-      <c r="L501"/>
-    </row>
-    <row r="502" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="502" spans="1:11" s="9" customFormat="1">
       <c r="A502" s="9">
         <v>24070073</v>
       </c>
@@ -24383,9 +23755,8 @@
         <v>3</v>
       </c>
       <c r="K502"/>
-      <c r="L502"/>
-    </row>
-    <row r="503" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="503" spans="1:11" s="9" customFormat="1">
       <c r="A503" s="9">
         <v>24070074</v>
       </c>
@@ -24420,7 +23791,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="504" spans="1:12" s="9" customFormat="1">
+    <row r="504" spans="1:11" s="9" customFormat="1">
       <c r="A504" s="9">
         <v>24070075</v>
       </c>
@@ -24446,9 +23817,8 @@
         <v>3</v>
       </c>
       <c r="K504" s="6"/>
-      <c r="L504" s="6"/>
-    </row>
-    <row r="505" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="505" spans="1:11" s="9" customFormat="1">
       <c r="A505" s="9">
         <v>24070076</v>
       </c>
@@ -24470,11 +23840,8 @@
       <c r="J505" s="9">
         <v>3</v>
       </c>
-      <c r="L505" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="506" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="506" spans="1:11" s="9" customFormat="1">
       <c r="A506" s="9">
         <v>24070078</v>
       </c>
@@ -24502,9 +23869,8 @@
         <v>3</v>
       </c>
       <c r="K506"/>
-      <c r="L506"/>
-    </row>
-    <row r="507" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="507" spans="1:11" s="9" customFormat="1">
       <c r="A507" s="9">
         <v>24070079</v>
       </c>
@@ -24526,11 +23892,8 @@
       <c r="J507" s="9">
         <v>3</v>
       </c>
-      <c r="L507" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="508" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="508" spans="1:11" s="9" customFormat="1">
       <c r="A508" s="9">
         <v>24070080</v>
       </c>
@@ -24564,9 +23927,8 @@
       <c r="K508" t="s">
         <v>748</v>
       </c>
-      <c r="L508"/>
-    </row>
-    <row r="509" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="509" spans="1:11" s="9" customFormat="1">
       <c r="A509" s="9">
         <v>24070081</v>
       </c>
@@ -24592,9 +23954,8 @@
         <v>3</v>
       </c>
       <c r="K509"/>
-      <c r="L509"/>
-    </row>
-    <row r="510" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="510" spans="1:11" s="9" customFormat="1">
       <c r="A510" s="9">
         <v>24070082</v>
       </c>
@@ -24617,7 +23978,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="511" spans="1:12" s="51" customFormat="1">
+    <row r="511" spans="1:11" s="51" customFormat="1">
       <c r="A511" s="9">
         <v>24070083</v>
       </c>
@@ -24645,9 +24006,8 @@
         <v>2</v>
       </c>
       <c r="K511" s="9"/>
-      <c r="L511" s="9"/>
-    </row>
-    <row r="512" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="512" spans="1:11" s="9" customFormat="1">
       <c r="A512" s="9">
         <v>24070084</v>
       </c>
@@ -24673,9 +24033,8 @@
         <v>3</v>
       </c>
       <c r="K512"/>
-      <c r="L512"/>
-    </row>
-    <row r="513" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="513" spans="1:11" s="9" customFormat="1">
       <c r="A513" s="9">
         <v>24070085</v>
       </c>
@@ -24709,9 +24068,8 @@
       <c r="K513" t="s">
         <v>1105</v>
       </c>
-      <c r="L513"/>
-    </row>
-    <row r="514" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="514" spans="1:11" s="9" customFormat="1">
       <c r="A514" s="9">
         <v>24070087</v>
       </c>
@@ -24740,7 +24098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="515" spans="1:12" s="9" customFormat="1">
+    <row r="515" spans="1:11" s="9" customFormat="1">
       <c r="A515" s="9">
         <v>24070088</v>
       </c>
@@ -24768,9 +24126,8 @@
         <v>3</v>
       </c>
       <c r="K515"/>
-      <c r="L515"/>
-    </row>
-    <row r="516" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="516" spans="1:11" s="9" customFormat="1">
       <c r="A516" s="9">
         <v>24070090</v>
       </c>
@@ -24792,11 +24149,8 @@
       <c r="J516" s="9">
         <v>3</v>
       </c>
-      <c r="L516" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="517" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="517" spans="1:11" s="33" customFormat="1">
       <c r="A517" s="9">
         <v>24070091</v>
       </c>
@@ -24830,9 +24184,8 @@
       <c r="K517" t="s">
         <v>1055</v>
       </c>
-      <c r="L517"/>
-    </row>
-    <row r="518" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="518" spans="1:11" s="9" customFormat="1">
       <c r="A518" s="9">
         <v>24070093</v>
       </c>
@@ -24866,9 +24219,8 @@
       <c r="K518" t="s">
         <v>1106</v>
       </c>
-      <c r="L518"/>
-    </row>
-    <row r="519" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="519" spans="1:11" s="9" customFormat="1">
       <c r="A519" s="9">
         <v>24070094</v>
       </c>
@@ -24902,9 +24254,8 @@
       <c r="K519" t="s">
         <v>1107</v>
       </c>
-      <c r="L519"/>
-    </row>
-    <row r="520" spans="1:12" s="51" customFormat="1">
+    </row>
+    <row r="520" spans="1:11" s="51" customFormat="1">
       <c r="A520" s="9">
         <v>24070095</v>
       </c>
@@ -24938,9 +24289,8 @@
       <c r="K520" t="s">
         <v>1108</v>
       </c>
-      <c r="L520"/>
-    </row>
-    <row r="521" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="521" spans="1:11" s="9" customFormat="1">
       <c r="A521" s="9">
         <v>24080001</v>
       </c>
@@ -24970,9 +24320,8 @@
         <v>2</v>
       </c>
       <c r="K521" s="14"/>
-      <c r="L521" s="14"/>
-    </row>
-    <row r="522" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="522" spans="1:11" s="9" customFormat="1">
       <c r="A522" s="9">
         <v>24080002</v>
       </c>
@@ -25006,9 +24355,8 @@
       <c r="K522" t="s">
         <v>1109</v>
       </c>
-      <c r="L522"/>
-    </row>
-    <row r="523" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="523" spans="1:11" s="9" customFormat="1">
       <c r="A523" s="9">
         <v>24080003</v>
       </c>
@@ -25034,9 +24382,8 @@
         <v>2</v>
       </c>
       <c r="K523"/>
-      <c r="L523"/>
-    </row>
-    <row r="524" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="524" spans="1:11" s="9" customFormat="1">
       <c r="A524" s="9">
         <v>24080004</v>
       </c>
@@ -25070,9 +24417,8 @@
       <c r="K524" t="s">
         <v>1110</v>
       </c>
-      <c r="L524"/>
-    </row>
-    <row r="525" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="525" spans="1:11" s="9" customFormat="1">
       <c r="A525" s="9">
         <v>24080005</v>
       </c>
@@ -25095,7 +24441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="526" spans="1:12" s="9" customFormat="1">
+    <row r="526" spans="1:11" s="9" customFormat="1">
       <c r="A526" s="9">
         <v>24080006</v>
       </c>
@@ -25123,9 +24469,8 @@
         <v>3</v>
       </c>
       <c r="K526"/>
-      <c r="L526"/>
-    </row>
-    <row r="527" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="527" spans="1:11" s="9" customFormat="1">
       <c r="A527" s="9">
         <v>24080007</v>
       </c>
@@ -25155,9 +24500,8 @@
         <v>3</v>
       </c>
       <c r="K527"/>
-      <c r="L527"/>
-    </row>
-    <row r="528" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="528" spans="1:11" s="9" customFormat="1">
       <c r="A528" s="9">
         <v>24080008</v>
       </c>
@@ -25185,9 +24529,8 @@
         <v>3</v>
       </c>
       <c r="K528"/>
-      <c r="L528"/>
-    </row>
-    <row r="529" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="529" spans="1:11" s="9" customFormat="1">
       <c r="A529" s="9">
         <v>24080009</v>
       </c>
@@ -25215,9 +24558,8 @@
         <v>3</v>
       </c>
       <c r="K529"/>
-      <c r="L529"/>
-    </row>
-    <row r="530" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="530" spans="1:11" s="9" customFormat="1">
       <c r="A530" s="9">
         <v>24080010</v>
       </c>
@@ -25240,7 +24582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="531" spans="1:12" s="9" customFormat="1">
+    <row r="531" spans="1:11" s="9" customFormat="1">
       <c r="A531" s="9">
         <v>24080011</v>
       </c>
@@ -25266,7 +24608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="532" spans="1:12" s="51" customFormat="1">
+    <row r="532" spans="1:11" s="51" customFormat="1">
       <c r="A532" s="9">
         <v>24080012</v>
       </c>
@@ -25294,9 +24636,8 @@
         <v>3</v>
       </c>
       <c r="K532"/>
-      <c r="L532"/>
-    </row>
-    <row r="533" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="533" spans="1:11" s="9" customFormat="1">
       <c r="A533" s="9">
         <v>24080013</v>
       </c>
@@ -25324,9 +24665,8 @@
         <v>3</v>
       </c>
       <c r="K533"/>
-      <c r="L533"/>
-    </row>
-    <row r="534" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="534" spans="1:11" s="9" customFormat="1">
       <c r="A534" s="9">
         <v>24080014</v>
       </c>
@@ -25348,11 +24688,8 @@
       <c r="J534" s="9">
         <v>3</v>
       </c>
-      <c r="L534" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="535" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="535" spans="1:11" s="9" customFormat="1">
       <c r="A535" s="9">
         <v>24080016</v>
       </c>
@@ -25386,9 +24723,8 @@
       <c r="K535" t="s">
         <v>742</v>
       </c>
-      <c r="L535"/>
-    </row>
-    <row r="536" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="536" spans="1:11" s="9" customFormat="1">
       <c r="A536" s="9">
         <v>24080017</v>
       </c>
@@ -25414,9 +24750,8 @@
         <v>3</v>
       </c>
       <c r="K536"/>
-      <c r="L536"/>
-    </row>
-    <row r="537" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="537" spans="1:11" s="9" customFormat="1">
       <c r="A537" s="9">
         <v>24080018</v>
       </c>
@@ -25442,9 +24777,8 @@
         <v>2</v>
       </c>
       <c r="K537"/>
-      <c r="L537"/>
-    </row>
-    <row r="538" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="538" spans="1:11" s="9" customFormat="1">
       <c r="A538" s="9">
         <v>24080019</v>
       </c>
@@ -25467,7 +24801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:12" s="9" customFormat="1">
+    <row r="539" spans="1:11" s="9" customFormat="1">
       <c r="A539" s="9">
         <v>24080020</v>
       </c>
@@ -25493,7 +24827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="540" spans="1:12" s="9" customFormat="1">
+    <row r="540" spans="1:11" s="9" customFormat="1">
       <c r="A540" s="9">
         <v>24080022</v>
       </c>
@@ -25521,9 +24855,8 @@
         <v>2</v>
       </c>
       <c r="K540"/>
-      <c r="L540"/>
-    </row>
-    <row r="541" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="541" spans="1:11" s="9" customFormat="1">
       <c r="A541" s="9">
         <v>24080023</v>
       </c>
@@ -25557,9 +24890,8 @@
       <c r="K541" t="s">
         <v>1112</v>
       </c>
-      <c r="L541"/>
-    </row>
-    <row r="542" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="542" spans="1:11" s="9" customFormat="1">
       <c r="A542" s="9">
         <v>24080024</v>
       </c>
@@ -25585,9 +24917,8 @@
         <v>3</v>
       </c>
       <c r="K542"/>
-      <c r="L542"/>
-    </row>
-    <row r="543" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="543" spans="1:11" s="9" customFormat="1">
       <c r="A543" s="9">
         <v>24080025</v>
       </c>
@@ -25615,9 +24946,8 @@
         <v>3</v>
       </c>
       <c r="K543"/>
-      <c r="L543"/>
-    </row>
-    <row r="544" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="544" spans="1:11" s="9" customFormat="1">
       <c r="A544" s="9">
         <v>24080026</v>
       </c>
@@ -25645,9 +24975,8 @@
         <v>2</v>
       </c>
       <c r="K544"/>
-      <c r="L544"/>
-    </row>
-    <row r="545" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="545" spans="1:11" s="9" customFormat="1">
       <c r="A545" s="9">
         <v>24080027</v>
       </c>
@@ -25670,7 +24999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="546" spans="1:12" s="9" customFormat="1" ht="15">
+    <row r="546" spans="1:11" s="9" customFormat="1" ht="15">
       <c r="A546" s="9">
         <v>24080028</v>
       </c>
@@ -25698,9 +25027,8 @@
         <v>3</v>
       </c>
       <c r="K546"/>
-      <c r="L546"/>
-    </row>
-    <row r="547" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="547" spans="1:11" s="9" customFormat="1">
       <c r="A547" s="9">
         <v>24080029</v>
       </c>
@@ -25722,11 +25050,8 @@
       <c r="J547" s="9">
         <v>3</v>
       </c>
-      <c r="L547" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="548" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="548" spans="1:11" s="9" customFormat="1">
       <c r="A548" s="9">
         <v>24080030</v>
       </c>
@@ -25752,7 +25077,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="549" spans="1:12" s="9" customFormat="1">
+    <row r="549" spans="1:11" s="9" customFormat="1">
       <c r="A549" s="9">
         <v>24080032</v>
       </c>
@@ -25778,7 +25103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="550" spans="1:12" s="52" customFormat="1">
+    <row r="550" spans="1:11" s="52" customFormat="1">
       <c r="A550" s="9">
         <v>24080033</v>
       </c>
@@ -25806,9 +25131,8 @@
         <v>3</v>
       </c>
       <c r="K550" s="9"/>
-      <c r="L550" s="9"/>
-    </row>
-    <row r="551" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="551" spans="1:11" s="9" customFormat="1">
       <c r="A551" s="9">
         <v>24080034</v>
       </c>
@@ -25834,9 +25158,8 @@
         <v>2</v>
       </c>
       <c r="K551"/>
-      <c r="L551"/>
-    </row>
-    <row r="552" spans="1:12" s="9" customFormat="1" ht="15">
+    </row>
+    <row r="552" spans="1:11" s="9" customFormat="1" ht="15">
       <c r="A552" s="9">
         <v>24080035</v>
       </c>
@@ -25864,9 +25187,8 @@
         <v>2</v>
       </c>
       <c r="K552"/>
-      <c r="L552"/>
-    </row>
-    <row r="553" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="553" spans="1:11" s="9" customFormat="1">
       <c r="A553" s="9">
         <v>24080036</v>
       </c>
@@ -25889,7 +25211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="554" spans="1:12" s="9" customFormat="1">
+    <row r="554" spans="1:11" s="9" customFormat="1">
       <c r="A554" s="9">
         <v>24080037</v>
       </c>
@@ -25911,11 +25233,8 @@
       <c r="J554" s="9">
         <v>3</v>
       </c>
-      <c r="L554" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="555" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="555" spans="1:11" s="9" customFormat="1">
       <c r="A555" s="9">
         <v>24080038</v>
       </c>
@@ -25938,7 +25257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="556" spans="1:12" s="9" customFormat="1">
+    <row r="556" spans="1:11" s="9" customFormat="1">
       <c r="A556" s="9">
         <v>24080039</v>
       </c>
@@ -25960,11 +25279,8 @@
       <c r="J556" s="9">
         <v>3</v>
       </c>
-      <c r="L556" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="557" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="557" spans="1:11" s="9" customFormat="1">
       <c r="A557" s="9">
         <v>24080041</v>
       </c>
@@ -25987,7 +25303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="558" spans="1:12" s="9" customFormat="1">
+    <row r="558" spans="1:11" s="9" customFormat="1">
       <c r="A558" s="9">
         <v>24080042</v>
       </c>
@@ -26013,7 +25329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="559" spans="1:12" s="9" customFormat="1">
+    <row r="559" spans="1:11" s="9" customFormat="1">
       <c r="A559" s="52">
         <v>24080043</v>
       </c>
@@ -26047,11 +25363,8 @@
       <c r="K559" s="52" t="s">
         <v>1961</v>
       </c>
-      <c r="L559" s="52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="560" spans="1:12" s="9" customFormat="1" ht="15">
+    </row>
+    <row r="560" spans="1:11" s="9" customFormat="1" ht="15">
       <c r="A560" s="9">
         <v>24080044</v>
       </c>
@@ -26077,9 +25390,8 @@
         <v>3</v>
       </c>
       <c r="K560"/>
-      <c r="L560"/>
-    </row>
-    <row r="561" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="561" spans="1:11" s="9" customFormat="1">
       <c r="A561" s="9">
         <v>24080045</v>
       </c>
@@ -26109,9 +25421,8 @@
         <v>2</v>
       </c>
       <c r="K561"/>
-      <c r="L561"/>
-    </row>
-    <row r="562" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="562" spans="1:11" s="33" customFormat="1">
       <c r="A562" s="9">
         <v>24080046</v>
       </c>
@@ -26137,9 +25448,8 @@
         <v>2</v>
       </c>
       <c r="K562" s="9"/>
-      <c r="L562" s="9"/>
-    </row>
-    <row r="563" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="563" spans="1:11" s="9" customFormat="1">
       <c r="A563" s="9">
         <v>24080047</v>
       </c>
@@ -26161,11 +25471,8 @@
       <c r="J563" s="9">
         <v>2</v>
       </c>
-      <c r="L563" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="564" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="564" spans="1:11" s="33" customFormat="1">
       <c r="A564" s="9">
         <v>24080048</v>
       </c>
@@ -26191,9 +25498,8 @@
         <v>3</v>
       </c>
       <c r="K564" s="9"/>
-      <c r="L564" s="9"/>
-    </row>
-    <row r="565" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="565" spans="1:11" s="33" customFormat="1">
       <c r="A565" s="9">
         <v>24080049</v>
       </c>
@@ -26221,9 +25527,8 @@
         <v>2</v>
       </c>
       <c r="K565"/>
-      <c r="L565"/>
-    </row>
-    <row r="566" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="566" spans="1:11" s="9" customFormat="1">
       <c r="A566" s="9">
         <v>24080050</v>
       </c>
@@ -26251,9 +25556,8 @@
         <v>3</v>
       </c>
       <c r="K566"/>
-      <c r="L566"/>
-    </row>
-    <row r="567" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="567" spans="1:11" s="9" customFormat="1">
       <c r="A567" s="9">
         <v>24080051</v>
       </c>
@@ -26276,7 +25580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="568" spans="1:12" s="9" customFormat="1">
+    <row r="568" spans="1:11" s="9" customFormat="1">
       <c r="A568" s="9">
         <v>24080052</v>
       </c>
@@ -26310,11 +25614,8 @@
       <c r="K568" s="9" t="s">
         <v>1774</v>
       </c>
-      <c r="L568" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="569" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="569" spans="1:11" s="9" customFormat="1">
       <c r="A569" s="9">
         <v>24080053</v>
       </c>
@@ -26342,9 +25643,8 @@
         <v>3</v>
       </c>
       <c r="K569"/>
-      <c r="L569"/>
-    </row>
-    <row r="570" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="570" spans="1:11" s="9" customFormat="1">
       <c r="A570" s="9">
         <v>24080054</v>
       </c>
@@ -26367,7 +25667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="571" spans="1:12" s="9" customFormat="1">
+    <row r="571" spans="1:11" s="9" customFormat="1">
       <c r="A571" s="9">
         <v>24080055</v>
       </c>
@@ -26401,9 +25701,8 @@
       <c r="K571" t="s">
         <v>1114</v>
       </c>
-      <c r="L571"/>
-    </row>
-    <row r="572" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="572" spans="1:11" s="9" customFormat="1">
       <c r="A572" s="9">
         <v>24080057</v>
       </c>
@@ -26425,11 +25724,8 @@
       <c r="J572" s="9">
         <v>3</v>
       </c>
-      <c r="L572" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="573" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="573" spans="1:11" s="9" customFormat="1">
       <c r="A573" s="9">
         <v>24080058</v>
       </c>
@@ -26455,7 +25751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="574" spans="1:12" s="9" customFormat="1" ht="12.9" customHeight="1">
+    <row r="574" spans="1:11" s="9" customFormat="1" ht="12.9" customHeight="1">
       <c r="A574" s="9">
         <v>24080059</v>
       </c>
@@ -26477,11 +25773,8 @@
       <c r="J574" s="9">
         <v>2</v>
       </c>
-      <c r="L574" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="575" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="575" spans="1:11" s="9" customFormat="1">
       <c r="A575" s="9">
         <v>24080060</v>
       </c>
@@ -26503,11 +25796,8 @@
       <c r="J575" s="9">
         <v>3</v>
       </c>
-      <c r="L575" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="576" spans="1:12" s="9" customFormat="1" ht="15">
+    </row>
+    <row r="576" spans="1:11" s="9" customFormat="1" ht="15">
       <c r="A576" s="9">
         <v>24080061</v>
       </c>
@@ -26541,9 +25831,8 @@
       <c r="K576" t="s">
         <v>1115</v>
       </c>
-      <c r="L576"/>
-    </row>
-    <row r="577" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="577" spans="1:11" s="9" customFormat="1">
       <c r="A577" s="9">
         <v>24080062</v>
       </c>
@@ -26577,9 +25866,8 @@
       <c r="K577" t="s">
         <v>1152</v>
       </c>
-      <c r="L577"/>
-    </row>
-    <row r="578" spans="1:12" s="9" customFormat="1" ht="15">
+    </row>
+    <row r="578" spans="1:11" s="9" customFormat="1" ht="15">
       <c r="A578" s="9">
         <v>24080063</v>
       </c>
@@ -26613,9 +25901,8 @@
       <c r="K578" t="s">
         <v>737</v>
       </c>
-      <c r="L578"/>
-    </row>
-    <row r="579" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="579" spans="1:11" s="9" customFormat="1">
       <c r="A579" s="9">
         <v>24080064</v>
       </c>
@@ -26641,7 +25928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="580" spans="1:12" s="9" customFormat="1">
+    <row r="580" spans="1:11" s="9" customFormat="1">
       <c r="A580" s="9">
         <v>24080065</v>
       </c>
@@ -26664,7 +25951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="581" spans="1:12" s="9" customFormat="1">
+    <row r="581" spans="1:11" s="9" customFormat="1">
       <c r="A581" s="9">
         <v>24090001</v>
       </c>
@@ -26698,9 +25985,8 @@
       <c r="K581" s="14" t="s">
         <v>1155</v>
       </c>
-      <c r="L581" s="14"/>
-    </row>
-    <row r="582" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="582" spans="1:11" s="9" customFormat="1">
       <c r="A582" s="9">
         <v>24090002</v>
       </c>
@@ -26722,11 +26008,8 @@
       <c r="J582" s="9">
         <v>3</v>
       </c>
-      <c r="L582" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="583" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="583" spans="1:11" s="9" customFormat="1">
       <c r="A583" s="9">
         <v>24090003</v>
       </c>
@@ -26756,9 +26039,8 @@
         <v>3</v>
       </c>
       <c r="K583"/>
-      <c r="L583"/>
-    </row>
-    <row r="584" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="584" spans="1:11" s="9" customFormat="1">
       <c r="A584" s="9">
         <v>24090004</v>
       </c>
@@ -26786,9 +26068,8 @@
         <v>3</v>
       </c>
       <c r="K584"/>
-      <c r="L584"/>
-    </row>
-    <row r="585" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="585" spans="1:11" s="9" customFormat="1">
       <c r="A585" s="9">
         <v>24090005</v>
       </c>
@@ -26816,9 +26097,8 @@
         <v>3</v>
       </c>
       <c r="K585"/>
-      <c r="L585"/>
-    </row>
-    <row r="586" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="586" spans="1:11" s="9" customFormat="1">
       <c r="A586" s="9">
         <v>24090006</v>
       </c>
@@ -26850,9 +26130,8 @@
       <c r="K586" t="s">
         <v>1204</v>
       </c>
-      <c r="L586"/>
-    </row>
-    <row r="587" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="587" spans="1:11" s="9" customFormat="1">
       <c r="A587" s="9">
         <v>24090007</v>
       </c>
@@ -26886,11 +26165,8 @@
       <c r="K587" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L587" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="588" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="588" spans="1:11" s="9" customFormat="1">
       <c r="A588" s="9">
         <v>24090008</v>
       </c>
@@ -26924,9 +26200,8 @@
       <c r="K588" t="s">
         <v>1158</v>
       </c>
-      <c r="L588"/>
-    </row>
-    <row r="589" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="589" spans="1:11" s="9" customFormat="1">
       <c r="A589" s="9">
         <v>24090009</v>
       </c>
@@ -26952,9 +26227,8 @@
         <v>3</v>
       </c>
       <c r="K589"/>
-      <c r="L589"/>
-    </row>
-    <row r="590" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="590" spans="1:11" s="9" customFormat="1">
       <c r="A590" s="9">
         <v>24090010</v>
       </c>
@@ -26976,11 +26250,8 @@
       <c r="J590" s="9">
         <v>3</v>
       </c>
-      <c r="L590" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="591" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="591" spans="1:11" s="9" customFormat="1">
       <c r="A591" s="9">
         <v>24090011</v>
       </c>
@@ -27006,9 +26277,8 @@
         <v>3</v>
       </c>
       <c r="K591"/>
-      <c r="L591"/>
-    </row>
-    <row r="592" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="592" spans="1:11" s="9" customFormat="1">
       <c r="A592" s="9">
         <v>24090012</v>
       </c>
@@ -27043,7 +26313,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="593" spans="1:12" s="9" customFormat="1">
+    <row r="593" spans="1:11" s="9" customFormat="1">
       <c r="A593" s="9">
         <v>24090013</v>
       </c>
@@ -27065,11 +26335,8 @@
       <c r="J593" s="9">
         <v>2</v>
       </c>
-      <c r="L593" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="594" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="594" spans="1:11" s="9" customFormat="1">
       <c r="A594" s="9">
         <v>24090014</v>
       </c>
@@ -27097,9 +26364,8 @@
         <v>3</v>
       </c>
       <c r="K594"/>
-      <c r="L594"/>
-    </row>
-    <row r="595" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="595" spans="1:11" s="9" customFormat="1">
       <c r="A595" s="9">
         <v>24090015</v>
       </c>
@@ -27125,7 +26391,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="596" spans="1:12" s="9" customFormat="1">
+    <row r="596" spans="1:11" s="9" customFormat="1">
       <c r="A596" s="9">
         <v>24090016</v>
       </c>
@@ -27159,9 +26425,8 @@
       <c r="K596" t="s">
         <v>733</v>
       </c>
-      <c r="L596"/>
-    </row>
-    <row r="597" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="597" spans="1:11" s="9" customFormat="1">
       <c r="A597" s="9">
         <v>24090018</v>
       </c>
@@ -27195,9 +26460,8 @@
       <c r="K597" t="s">
         <v>1109</v>
       </c>
-      <c r="L597"/>
-    </row>
-    <row r="598" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="598" spans="1:11" s="9" customFormat="1">
       <c r="A598" s="9">
         <v>24090019</v>
       </c>
@@ -27225,9 +26489,8 @@
         <v>3</v>
       </c>
       <c r="K598"/>
-      <c r="L598"/>
-    </row>
-    <row r="599" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="599" spans="1:11" s="9" customFormat="1">
       <c r="A599" s="9">
         <v>24090020</v>
       </c>
@@ -27257,9 +26520,8 @@
         <v>3</v>
       </c>
       <c r="K599"/>
-      <c r="L599"/>
-    </row>
-    <row r="600" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="600" spans="1:11" s="9" customFormat="1">
       <c r="A600" s="9">
         <v>24090021</v>
       </c>
@@ -27287,9 +26549,8 @@
         <v>3</v>
       </c>
       <c r="K600"/>
-      <c r="L600"/>
-    </row>
-    <row r="601" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="601" spans="1:11" s="9" customFormat="1">
       <c r="A601" s="9">
         <v>24090022</v>
       </c>
@@ -27317,9 +26578,8 @@
         <v>3</v>
       </c>
       <c r="K601"/>
-      <c r="L601"/>
-    </row>
-    <row r="602" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="602" spans="1:11" s="9" customFormat="1">
       <c r="A602" s="9">
         <v>24090023</v>
       </c>
@@ -27347,9 +26607,8 @@
         <v>3</v>
       </c>
       <c r="K602"/>
-      <c r="L602"/>
-    </row>
-    <row r="603" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="603" spans="1:11" s="9" customFormat="1">
       <c r="A603" s="9">
         <v>24090024</v>
       </c>
@@ -27383,9 +26642,8 @@
       <c r="K603" t="s">
         <v>1162</v>
       </c>
-      <c r="L603"/>
-    </row>
-    <row r="604" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="604" spans="1:11" s="9" customFormat="1">
       <c r="A604" s="9">
         <v>24090025</v>
       </c>
@@ -27413,9 +26671,8 @@
         <v>3</v>
       </c>
       <c r="K604"/>
-      <c r="L604"/>
-    </row>
-    <row r="605" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="605" spans="1:11" s="9" customFormat="1">
       <c r="A605" s="9">
         <v>24090026</v>
       </c>
@@ -27443,9 +26700,8 @@
         <v>3</v>
       </c>
       <c r="K605"/>
-      <c r="L605"/>
-    </row>
-    <row r="606" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="606" spans="1:11" s="9" customFormat="1">
       <c r="A606" s="9">
         <v>24090027</v>
       </c>
@@ -27480,7 +26736,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="607" spans="1:12" s="9" customFormat="1">
+    <row r="607" spans="1:11" s="9" customFormat="1">
       <c r="A607" s="9">
         <v>24090028</v>
       </c>
@@ -27508,9 +26764,8 @@
         <v>3</v>
       </c>
       <c r="K607"/>
-      <c r="L607"/>
-    </row>
-    <row r="608" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="608" spans="1:11" s="9" customFormat="1">
       <c r="A608" s="9">
         <v>24090029</v>
       </c>
@@ -27538,9 +26793,8 @@
         <v>3</v>
       </c>
       <c r="K608"/>
-      <c r="L608"/>
-    </row>
-    <row r="609" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="609" spans="1:11" s="9" customFormat="1">
       <c r="A609" s="9">
         <v>24090030</v>
       </c>
@@ -27569,7 +26823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="610" spans="1:12" s="9" customFormat="1">
+    <row r="610" spans="1:11" s="9" customFormat="1">
       <c r="A610" s="9">
         <v>24090032</v>
       </c>
@@ -27597,9 +26851,8 @@
         <v>3</v>
       </c>
       <c r="K610"/>
-      <c r="L610"/>
-    </row>
-    <row r="611" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="611" spans="1:11" s="9" customFormat="1">
       <c r="A611" s="9">
         <v>24090033</v>
       </c>
@@ -27627,9 +26880,8 @@
         <v>3</v>
       </c>
       <c r="K611"/>
-      <c r="L611"/>
-    </row>
-    <row r="612" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="612" spans="1:11" s="9" customFormat="1">
       <c r="A612" s="9">
         <v>24090034</v>
       </c>
@@ -27657,9 +26909,8 @@
         <v>3</v>
       </c>
       <c r="K612"/>
-      <c r="L612"/>
-    </row>
-    <row r="613" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="613" spans="1:11" s="9" customFormat="1">
       <c r="A613" s="9">
         <v>24090036</v>
       </c>
@@ -27685,9 +26936,8 @@
         <v>3</v>
       </c>
       <c r="K613"/>
-      <c r="L613"/>
-    </row>
-    <row r="614" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="614" spans="1:11" s="9" customFormat="1">
       <c r="A614" s="9">
         <v>24090037</v>
       </c>
@@ -27713,9 +26963,8 @@
         <v>3</v>
       </c>
       <c r="K614"/>
-      <c r="L614"/>
-    </row>
-    <row r="615" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="615" spans="1:11" s="9" customFormat="1">
       <c r="A615" s="9">
         <v>24090038</v>
       </c>
@@ -27737,11 +26986,8 @@
       <c r="J615" s="9">
         <v>3</v>
       </c>
-      <c r="L615" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="616" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="616" spans="1:11" s="9" customFormat="1">
       <c r="A616" s="9">
         <v>24090039</v>
       </c>
@@ -27767,9 +27013,8 @@
         <v>3</v>
       </c>
       <c r="K616"/>
-      <c r="L616"/>
-    </row>
-    <row r="617" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="617" spans="1:11" s="33" customFormat="1">
       <c r="A617" s="9">
         <v>24090040</v>
       </c>
@@ -27797,9 +27042,8 @@
         <v>2</v>
       </c>
       <c r="K617"/>
-      <c r="L617"/>
-    </row>
-    <row r="618" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="618" spans="1:11" s="9" customFormat="1">
       <c r="A618" s="9">
         <v>24090041</v>
       </c>
@@ -27822,7 +27066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="619" spans="1:12" s="9" customFormat="1">
+    <row r="619" spans="1:11" s="9" customFormat="1">
       <c r="A619" s="9">
         <v>24090042</v>
       </c>
@@ -27850,9 +27094,8 @@
         <v>3</v>
       </c>
       <c r="K619"/>
-      <c r="L619"/>
-    </row>
-    <row r="620" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="620" spans="1:11" s="9" customFormat="1">
       <c r="A620" s="9">
         <v>24090043</v>
       </c>
@@ -27882,9 +27125,8 @@
         <v>3</v>
       </c>
       <c r="K620"/>
-      <c r="L620"/>
-    </row>
-    <row r="621" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="621" spans="1:11" s="9" customFormat="1">
       <c r="A621" s="9">
         <v>24090044</v>
       </c>
@@ -27912,9 +27154,8 @@
         <v>3</v>
       </c>
       <c r="K621"/>
-      <c r="L621"/>
-    </row>
-    <row r="622" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="622" spans="1:11" s="9" customFormat="1">
       <c r="A622" s="9">
         <v>24090045</v>
       </c>
@@ -27942,9 +27183,8 @@
         <v>3</v>
       </c>
       <c r="K622"/>
-      <c r="L622"/>
-    </row>
-    <row r="623" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="623" spans="1:11" s="9" customFormat="1">
       <c r="A623" s="9">
         <v>24090046</v>
       </c>
@@ -27978,9 +27218,8 @@
       <c r="K623" t="s">
         <v>1188</v>
       </c>
-      <c r="L623"/>
-    </row>
-    <row r="624" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="624" spans="1:11" s="9" customFormat="1">
       <c r="A624" s="9">
         <v>24090047</v>
       </c>
@@ -28015,7 +27254,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="625" spans="1:12" s="9" customFormat="1">
+    <row r="625" spans="1:11" s="9" customFormat="1">
       <c r="A625" s="9">
         <v>24090048</v>
       </c>
@@ -28043,9 +27282,8 @@
         <v>3</v>
       </c>
       <c r="K625"/>
-      <c r="L625"/>
-    </row>
-    <row r="626" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="626" spans="1:11" s="9" customFormat="1">
       <c r="A626" s="9">
         <v>24090049</v>
       </c>
@@ -28073,9 +27311,8 @@
         <v>3</v>
       </c>
       <c r="K626"/>
-      <c r="L626"/>
-    </row>
-    <row r="627" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="627" spans="1:11" s="9" customFormat="1">
       <c r="A627" s="9">
         <v>24090050</v>
       </c>
@@ -28103,9 +27340,8 @@
         <v>3</v>
       </c>
       <c r="K627"/>
-      <c r="L627"/>
-    </row>
-    <row r="628" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="628" spans="1:11" s="9" customFormat="1">
       <c r="A628" s="9">
         <v>24090051</v>
       </c>
@@ -28133,9 +27369,8 @@
         <v>3</v>
       </c>
       <c r="K628"/>
-      <c r="L628"/>
-    </row>
-    <row r="629" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="629" spans="1:11" s="9" customFormat="1">
       <c r="A629" s="9">
         <v>24090052</v>
       </c>
@@ -28161,9 +27396,8 @@
         <v>3</v>
       </c>
       <c r="K629"/>
-      <c r="L629"/>
-    </row>
-    <row r="630" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="630" spans="1:11" s="9" customFormat="1">
       <c r="A630" s="9">
         <v>24090053</v>
       </c>
@@ -28197,9 +27431,8 @@
       <c r="K630" t="s">
         <v>1191</v>
       </c>
-      <c r="L630"/>
-    </row>
-    <row r="631" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="631" spans="1:11" s="9" customFormat="1">
       <c r="A631" s="9">
         <v>24090054</v>
       </c>
@@ -28225,9 +27458,8 @@
         <v>3</v>
       </c>
       <c r="K631"/>
-      <c r="L631"/>
-    </row>
-    <row r="632" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="632" spans="1:11" s="33" customFormat="1">
       <c r="A632" s="9">
         <v>24090055</v>
       </c>
@@ -28253,9 +27485,8 @@
         <v>2</v>
       </c>
       <c r="K632"/>
-      <c r="L632"/>
-    </row>
-    <row r="633" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="633" spans="1:11" s="9" customFormat="1">
       <c r="A633" s="9">
         <v>24090056</v>
       </c>
@@ -28285,9 +27516,8 @@
       <c r="K633" s="6" t="s">
         <v>1208</v>
       </c>
-      <c r="L633"/>
-    </row>
-    <row r="634" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="634" spans="1:11" s="9" customFormat="1">
       <c r="A634" s="9">
         <v>24090058</v>
       </c>
@@ -28313,9 +27543,8 @@
         <v>3</v>
       </c>
       <c r="K634"/>
-      <c r="L634"/>
-    </row>
-    <row r="635" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="635" spans="1:11" s="9" customFormat="1">
       <c r="A635" s="9">
         <v>24090059</v>
       </c>
@@ -28341,9 +27570,8 @@
         <v>3</v>
       </c>
       <c r="K635"/>
-      <c r="L635"/>
-    </row>
-    <row r="636" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="636" spans="1:11" s="9" customFormat="1">
       <c r="A636" s="9">
         <v>24090060</v>
       </c>
@@ -28371,9 +27599,8 @@
         <v>3</v>
       </c>
       <c r="K636"/>
-      <c r="L636"/>
-    </row>
-    <row r="637" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="637" spans="1:11" s="9" customFormat="1">
       <c r="A637" s="9">
         <v>24090061</v>
       </c>
@@ -28408,7 +27635,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="638" spans="1:12" s="9" customFormat="1">
+    <row r="638" spans="1:11" s="9" customFormat="1">
       <c r="A638" s="9">
         <v>24090062</v>
       </c>
@@ -28438,9 +27665,8 @@
         <v>3</v>
       </c>
       <c r="K638"/>
-      <c r="L638"/>
-    </row>
-    <row r="639" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="639" spans="1:11" s="9" customFormat="1">
       <c r="A639" s="9">
         <v>24090063</v>
       </c>
@@ -28474,9 +27700,8 @@
       <c r="K639" t="s">
         <v>737</v>
       </c>
-      <c r="L639"/>
-    </row>
-    <row r="640" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="640" spans="1:11" s="9" customFormat="1">
       <c r="A640" s="9">
         <v>24090064</v>
       </c>
@@ -28504,9 +27729,8 @@
         <v>3</v>
       </c>
       <c r="K640"/>
-      <c r="L640"/>
-    </row>
-    <row r="641" spans="1:12" s="52" customFormat="1">
+    </row>
+    <row r="641" spans="1:11" s="52" customFormat="1">
       <c r="A641" s="9">
         <v>24090065</v>
       </c>
@@ -28540,9 +27764,8 @@
       <c r="K641" t="s">
         <v>1167</v>
       </c>
-      <c r="L641"/>
-    </row>
-    <row r="642" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="642" spans="1:11" s="9" customFormat="1">
       <c r="A642" s="9">
         <v>24090066</v>
       </c>
@@ -28577,7 +27800,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="643" spans="1:12" s="9" customFormat="1">
+    <row r="643" spans="1:11" s="9" customFormat="1">
       <c r="A643" s="9">
         <v>24090067</v>
       </c>
@@ -28605,9 +27828,8 @@
         <v>3</v>
       </c>
       <c r="K643"/>
-      <c r="L643"/>
-    </row>
-    <row r="644" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="644" spans="1:11" s="9" customFormat="1">
       <c r="A644" s="9">
         <v>24090068</v>
       </c>
@@ -28633,7 +27855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="645" spans="1:12" s="9" customFormat="1">
+    <row r="645" spans="1:11" s="9" customFormat="1">
       <c r="A645" s="9">
         <v>24090069</v>
       </c>
@@ -28661,9 +27883,8 @@
         <v>2</v>
       </c>
       <c r="K645"/>
-      <c r="L645"/>
-    </row>
-    <row r="646" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="646" spans="1:11" s="9" customFormat="1">
       <c r="A646" s="9">
         <v>24090070</v>
       </c>
@@ -28689,7 +27910,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="647" spans="1:12" s="33" customFormat="1">
+    <row r="647" spans="1:11" s="33" customFormat="1">
       <c r="A647" s="9">
         <v>24090071</v>
       </c>
@@ -28717,9 +27938,8 @@
         <v>3</v>
       </c>
       <c r="K647" s="9"/>
-      <c r="L647" s="9"/>
-    </row>
-    <row r="648" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="648" spans="1:11" s="9" customFormat="1">
       <c r="A648" s="9">
         <v>24090072</v>
       </c>
@@ -28753,9 +27973,8 @@
       <c r="K648" t="s">
         <v>737</v>
       </c>
-      <c r="L648"/>
-    </row>
-    <row r="649" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="649" spans="1:11" s="9" customFormat="1">
       <c r="A649" s="9">
         <v>24090073</v>
       </c>
@@ -28789,9 +28008,8 @@
       <c r="K649" t="s">
         <v>1202</v>
       </c>
-      <c r="L649"/>
-    </row>
-    <row r="650" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="650" spans="1:11" s="9" customFormat="1">
       <c r="A650" s="9">
         <v>24090075</v>
       </c>
@@ -28817,9 +28035,8 @@
         <v>3</v>
       </c>
       <c r="K650"/>
-      <c r="L650"/>
-    </row>
-    <row r="651" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="651" spans="1:11" s="9" customFormat="1">
       <c r="A651" s="9">
         <v>24090076</v>
       </c>
@@ -28853,11 +28070,8 @@
       <c r="K651" s="9" t="s">
         <v>1763</v>
       </c>
-      <c r="L651" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="652" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="652" spans="1:11" s="9" customFormat="1">
       <c r="A652" s="9">
         <v>24090077</v>
       </c>
@@ -28891,9 +28105,8 @@
       <c r="K652" t="s">
         <v>1169</v>
       </c>
-      <c r="L652"/>
-    </row>
-    <row r="653" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="653" spans="1:11" s="9" customFormat="1">
       <c r="A653" s="9">
         <v>24010001</v>
       </c>
@@ -28927,11 +28140,8 @@
       <c r="K653" s="32" t="s">
         <v>768</v>
       </c>
-      <c r="L653" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="654" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="654" spans="1:11" s="9" customFormat="1">
       <c r="A654" s="9">
         <v>24010043</v>
       </c>
@@ -28965,11 +28175,8 @@
       <c r="K654" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="L654" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="655" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="655" spans="1:11" s="33" customFormat="1">
       <c r="A655" s="9">
         <v>24010049</v>
       </c>
@@ -29003,11 +28210,8 @@
       <c r="K655" s="9" t="s">
         <v>2173</v>
       </c>
-      <c r="L655" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="656" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="656" spans="1:11" s="9" customFormat="1">
       <c r="A656" s="9">
         <v>24010088</v>
       </c>
@@ -29041,11 +28245,8 @@
       <c r="K656" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L656" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="657" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="657" spans="1:11" s="9" customFormat="1">
       <c r="A657" s="9">
         <v>24010092</v>
       </c>
@@ -29079,11 +28280,8 @@
       <c r="K657" s="9" t="s">
         <v>2178</v>
       </c>
-      <c r="L657" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="658" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="658" spans="1:11" s="33" customFormat="1">
       <c r="A658" s="9">
         <v>24010104</v>
       </c>
@@ -29117,11 +28315,8 @@
       <c r="K658" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L658" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="659" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="659" spans="1:11" s="9" customFormat="1">
       <c r="A659" s="9">
         <v>24020004</v>
       </c>
@@ -29155,11 +28350,8 @@
       <c r="K659" s="9" t="s">
         <v>959</v>
       </c>
-      <c r="L659" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="660" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="660" spans="1:11" s="9" customFormat="1">
       <c r="A660" s="9">
         <v>24020020</v>
       </c>
@@ -29193,11 +28385,8 @@
       <c r="K660" s="9" t="s">
         <v>2185</v>
       </c>
-      <c r="L660" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="661" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="661" spans="1:11" s="9" customFormat="1">
       <c r="A661" s="9">
         <v>24020043</v>
       </c>
@@ -29219,11 +28408,8 @@
       <c r="J661" s="9">
         <v>3</v>
       </c>
-      <c r="L661" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="662" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="662" spans="1:11" s="33" customFormat="1">
       <c r="A662" s="33">
         <v>24020048</v>
       </c>
@@ -29254,11 +28440,8 @@
       <c r="K662" s="33" t="s">
         <v>959</v>
       </c>
-      <c r="L662" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="663" spans="1:12" s="9" customFormat="1" ht="15">
+    </row>
+    <row r="663" spans="1:11" s="9" customFormat="1" ht="15">
       <c r="A663" s="9">
         <v>24020060</v>
       </c>
@@ -29292,11 +28475,8 @@
       <c r="K663" s="9" t="s">
         <v>959</v>
       </c>
-      <c r="L663" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="664" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="664" spans="1:11" s="33" customFormat="1">
       <c r="A664" s="33">
         <v>24020061</v>
       </c>
@@ -29321,11 +28501,8 @@
       <c r="J664" s="33">
         <v>3</v>
       </c>
-      <c r="L664" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="665" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="665" spans="1:11" s="9" customFormat="1">
       <c r="A665" s="9">
         <v>24030106</v>
       </c>
@@ -29347,11 +28524,8 @@
       <c r="J665" s="9">
         <v>3</v>
       </c>
-      <c r="L665" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="666" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="666" spans="1:11" s="9" customFormat="1">
       <c r="A666" s="9">
         <v>24040016</v>
       </c>
@@ -29385,11 +28559,8 @@
       <c r="K666" s="9" t="s">
         <v>788</v>
       </c>
-      <c r="L666" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="667" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="667" spans="1:11" s="33" customFormat="1">
       <c r="A667" s="33">
         <v>24040041</v>
       </c>
@@ -29423,11 +28594,8 @@
       <c r="K667" s="33" t="s">
         <v>2202</v>
       </c>
-      <c r="L667" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="668" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="668" spans="1:11" s="9" customFormat="1">
       <c r="A668" s="9">
         <v>24040043</v>
       </c>
@@ -29461,11 +28629,8 @@
       <c r="K668" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L668" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="669" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="669" spans="1:11" s="33" customFormat="1">
       <c r="A669" s="33">
         <v>24050013</v>
       </c>
@@ -29499,11 +28664,8 @@
       <c r="K669" s="33" t="s">
         <v>2209</v>
       </c>
-      <c r="L669" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="670" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="670" spans="1:11" s="9" customFormat="1">
       <c r="A670" s="9">
         <v>24050030</v>
       </c>
@@ -29537,11 +28699,8 @@
       <c r="K670" s="9" t="s">
         <v>1911</v>
       </c>
-      <c r="L670" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="671" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="671" spans="1:11" s="9" customFormat="1">
       <c r="A671" s="9">
         <v>24050048</v>
       </c>
@@ -29563,11 +28722,8 @@
       <c r="J671" s="9">
         <v>3</v>
       </c>
-      <c r="L671" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="672" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="672" spans="1:11" s="9" customFormat="1">
       <c r="A672" s="9">
         <v>24050049</v>
       </c>
@@ -29589,11 +28745,8 @@
       <c r="J672" s="9">
         <v>3</v>
       </c>
-      <c r="L672" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="673" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="673" spans="1:11" s="33" customFormat="1">
       <c r="A673" s="33">
         <v>24050083</v>
       </c>
@@ -29618,11 +28771,8 @@
       <c r="J673" s="33">
         <v>3</v>
       </c>
-      <c r="L673" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="674" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="674" spans="1:11" s="9" customFormat="1">
       <c r="A674" s="9">
         <v>24050115</v>
       </c>
@@ -29644,11 +28794,8 @@
       <c r="J674" s="9">
         <v>3</v>
       </c>
-      <c r="L674" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="675" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="675" spans="1:11" s="9" customFormat="1">
       <c r="A675" s="9">
         <v>24050128</v>
       </c>
@@ -29670,11 +28817,8 @@
       <c r="J675" s="9">
         <v>3</v>
       </c>
-      <c r="L675" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="676" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="676" spans="1:11" s="9" customFormat="1">
       <c r="A676" s="9">
         <v>24050160</v>
       </c>
@@ -29708,11 +28852,8 @@
       <c r="K676" s="9" t="s">
         <v>2226</v>
       </c>
-      <c r="L676" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="677" spans="1:12" s="33" customFormat="1">
+    </row>
+    <row r="677" spans="1:11" s="33" customFormat="1">
       <c r="A677" s="33">
         <v>24060010</v>
       </c>
@@ -29746,11 +28887,8 @@
       <c r="K677" s="33" t="s">
         <v>2231</v>
       </c>
-      <c r="L677" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="678" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="678" spans="1:11" s="9" customFormat="1">
       <c r="A678" s="9">
         <v>24060020</v>
       </c>
@@ -29784,11 +28922,8 @@
       <c r="K678" s="9" t="s">
         <v>1169</v>
       </c>
-      <c r="L678" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="679" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="679" spans="1:11" s="9" customFormat="1">
       <c r="A679" s="9">
         <v>24070026</v>
       </c>
@@ -29822,11 +28957,8 @@
       <c r="K679" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="L679" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="680" spans="1:12" s="9" customFormat="1" ht="15">
+    </row>
+    <row r="680" spans="1:11" s="9" customFormat="1" ht="15">
       <c r="A680" s="9">
         <v>24070045</v>
       </c>
@@ -29860,11 +28992,8 @@
       <c r="K680" s="9" t="s">
         <v>2238</v>
       </c>
-      <c r="L680" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="681" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="681" spans="1:11" s="9" customFormat="1">
       <c r="A681" s="9">
         <v>24070058</v>
       </c>
@@ -29886,11 +29015,8 @@
       <c r="J681" s="9">
         <v>3</v>
       </c>
-      <c r="L681" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="682" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="682" spans="1:11" s="9" customFormat="1">
       <c r="A682" s="9">
         <v>24090057</v>
       </c>
@@ -29912,11 +29038,8 @@
       <c r="J682" s="9">
         <v>3</v>
       </c>
-      <c r="L682" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="683" spans="1:12" s="9" customFormat="1">
+    </row>
+    <row r="683" spans="1:11" s="9" customFormat="1">
       <c r="A683" s="9">
         <v>24090017</v>
       </c>
@@ -29939,23 +29062,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="684" spans="1:12">
+    <row r="684" spans="1:11">
       <c r="A684" s="20"/>
       <c r="B684"/>
     </row>
-    <row r="685" spans="1:12">
+    <row r="685" spans="1:11">
       <c r="A685" s="20"/>
       <c r="B685"/>
     </row>
-    <row r="686" spans="1:12">
+    <row r="686" spans="1:11">
       <c r="A686" s="20"/>
       <c r="B686"/>
     </row>
-    <row r="687" spans="1:12">
+    <row r="687" spans="1:11">
       <c r="A687" s="20"/>
       <c r="B687"/>
     </row>
-    <row r="688" spans="1:12">
+    <row r="688" spans="1:11">
       <c r="A688" s="20"/>
       <c r="B688"/>
     </row>
@@ -29973,7 +29096,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:A695" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L652">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K652">
     <sortCondition ref="A1:A652"/>
   </sortState>
   <phoneticPr fontId="8" type="noConversion"/>
